--- a/Data/LookupData/LookupMenuBreakdown.xlsx
+++ b/Data/LookupData/LookupMenuBreakdown.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="255">
   <si>
     <t>Item name updated</t>
   </si>
@@ -767,10 +767,22 @@
     <t>Lamb Kebab Bowl - Catering</t>
   </si>
   <si>
+    <t>Tamarind Lamb Kebab</t>
+  </si>
+  <si>
     <t>Lamb Kebab Bowl - In House</t>
   </si>
   <si>
+    <t>Coconut Harvest Bowl</t>
+  </si>
+  <si>
+    <t>Spicy Chicken + Avocado</t>
+  </si>
+  <si>
     <t>Cauliflower + Quinoa</t>
+  </si>
+  <si>
+    <t>Tandoori Chicken Ranch Wrap</t>
   </si>
   <si>
     <t>Tandoori Tasting Bundle</t>
@@ -780,96 +792,6 @@
   </si>
   <si>
     <t>Iced Oat Masala Chai for a Group - 1/2 Gallon</t>
-  </si>
-  <si>
-    <t>Paneer Butter Masala - Catering</t>
-  </si>
-  <si>
-    <t>Paneer Butter Masala - In House</t>
-  </si>
-  <si>
-    <t>Paneer Tikka Bowl - Catering</t>
-  </si>
-  <si>
-    <t>Paneer Tikka Bowl - In House</t>
-  </si>
-  <si>
-    <t>Saag Paneer - Catering</t>
-  </si>
-  <si>
-    <t>Saag Paneer - In House</t>
-  </si>
-  <si>
-    <t>BYO Salad Bowl - Catering</t>
-  </si>
-  <si>
-    <t>BYO Salad Bowl - In House</t>
-  </si>
-  <si>
-    <t>Sharebite Chicken Tikka Bowl</t>
-  </si>
-  <si>
-    <t>Sharebite Spicy Chili Chicken Bowl</t>
-  </si>
-  <si>
-    <t>Sharebite Tandoori Paneer Bowl</t>
-  </si>
-  <si>
-    <t>Spicy Chicken Burrito - In House</t>
-  </si>
-  <si>
-    <t>Spicy Chili Chicken Bowl - Catering</t>
-  </si>
-  <si>
-    <t>Spicy Chili Chicken Bowl - In House</t>
-  </si>
-  <si>
-    <t>Tandoori Paneer Burrito - Catering</t>
-  </si>
-  <si>
-    <t>Tandoori Paneer Burrito - In House</t>
-  </si>
-  <si>
-    <t>Paneer Makhani - Old</t>
-  </si>
-  <si>
-    <t>Chicken Tikka Masala - old</t>
-  </si>
-  <si>
-    <t>Saag Paneer - old</t>
-  </si>
-  <si>
-    <t>Cater Cow Tandoori Paneer Bowl</t>
-  </si>
-  <si>
-    <t>Sharebite Cauliflower + Quinoa Bowl</t>
-  </si>
-  <si>
-    <t>Maine Root Fountain Soda - In House</t>
-  </si>
-  <si>
-    <t>Paneer Tikka Masala - In House</t>
-  </si>
-  <si>
-    <t>Lamb Kofta Korma - In House</t>
-  </si>
-  <si>
-    <t>Chicken Curry - In House</t>
-  </si>
-  <si>
-    <t>Saag Chole - In House</t>
-  </si>
-  <si>
-    <t>Homemade Juice - In House</t>
-  </si>
-  <si>
-    <t>Pick 2 Combo Plate - In House</t>
-  </si>
-  <si>
-    <t>Cauliflower + Quinoa - In House</t>
-  </si>
-  <si>
-    <t>Coconut Veggie Curry - In House</t>
   </si>
 </sst>
 </file>
@@ -9263,8 +9185,12 @@
         <v>229</v>
       </c>
       <c r="F181" s="2"/>
-      <c r="G181" s="2"/>
-      <c r="H181" s="2"/>
+      <c r="G181" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
@@ -9286,7 +9212,7 @@
     </row>
     <row r="182" ht="68.75" spans="1:26">
       <c r="A182" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>39</v>
@@ -9299,8 +9225,12 @@
         <v>230</v>
       </c>
       <c r="F182" s="2"/>
-      <c r="G182" s="2"/>
-      <c r="H182" s="2"/>
+      <c r="G182" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="I182" s="2"/>
       <c r="J182" s="2"/>
       <c r="K182" s="2"/>
@@ -9335,8 +9265,12 @@
         <v>231</v>
       </c>
       <c r="F183" s="2"/>
-      <c r="G183" s="2"/>
-      <c r="H183" s="2"/>
+      <c r="G183" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="I183" s="2"/>
       <c r="J183" s="2"/>
       <c r="K183" s="2"/>
@@ -9356,7 +9290,7 @@
       <c r="Y183" s="2"/>
       <c r="Z183" s="2"/>
     </row>
-    <row r="184" ht="44.75" spans="1:26">
+    <row r="184" ht="58.75" spans="1:26">
       <c r="A184" s="1" t="s">
         <v>120</v>
       </c>
@@ -9365,14 +9299,18 @@
       </c>
       <c r="C184" s="2"/>
       <c r="D184" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F184" s="2"/>
-      <c r="G184" s="2"/>
-      <c r="H184" s="2"/>
+      <c r="G184" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="I184" s="2"/>
       <c r="J184" s="2"/>
       <c r="K184" s="2"/>
@@ -9653,10 +9591,10 @@
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
@@ -9689,7 +9627,7 @@
       </c>
       <c r="C193" s="2"/>
       <c r="D193" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>106</v>
@@ -9760,8 +9698,12 @@
         <v>127</v>
       </c>
       <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
-      <c r="E195" s="2"/>
+      <c r="D195" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
@@ -9784,7 +9726,7 @@
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
     </row>
-    <row r="196" ht="34.75" spans="1:26">
+    <row r="196" ht="44.75" spans="1:26">
       <c r="A196" s="1" t="s">
         <v>106</v>
       </c>
@@ -9792,8 +9734,12 @@
         <v>106</v>
       </c>
       <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
+      <c r="D196" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
@@ -9816,7 +9762,7 @@
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
     </row>
-    <row r="197" ht="34.75" spans="1:26">
+    <row r="197" ht="44.75" spans="1:26">
       <c r="A197" s="1" t="s">
         <v>106</v>
       </c>
@@ -9824,8 +9770,12 @@
         <v>106</v>
       </c>
       <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
-      <c r="E197" s="2"/>
+      <c r="D197" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
@@ -9848,7 +9798,7 @@
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
     </row>
-    <row r="198" ht="34.75" spans="1:26">
+    <row r="198" ht="58.75" spans="1:26">
       <c r="A198" s="1" t="s">
         <v>106</v>
       </c>
@@ -9856,8 +9806,12 @@
         <v>106</v>
       </c>
       <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
-      <c r="E198" s="2"/>
+      <c r="D198" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
@@ -9944,13 +9898,9 @@
       <c r="Y200" s="2"/>
       <c r="Z200" s="2"/>
     </row>
-    <row r="201" ht="51.75" spans="1:26">
-      <c r="A201" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>130</v>
-      </c>
+    <row r="201" ht="17.55" spans="1:26">
+      <c r="A201" s="2"/>
+      <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
@@ -9976,13 +9926,9 @@
       <c r="Y201" s="2"/>
       <c r="Z201" s="2"/>
     </row>
-    <row r="202" ht="51.75" spans="1:26">
-      <c r="A202" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>125</v>
-      </c>
+    <row r="202" ht="17.55" spans="1:26">
+      <c r="A202" s="2"/>
+      <c r="B202" s="2"/>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
@@ -10008,13 +9954,9 @@
       <c r="Y202" s="2"/>
       <c r="Z202" s="2"/>
     </row>
-    <row r="203" ht="51.75" spans="1:26">
-      <c r="A203" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>125</v>
-      </c>
+    <row r="203" ht="17.55" spans="1:26">
+      <c r="A203" s="2"/>
+      <c r="B203" s="2"/>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
@@ -10040,13 +9982,9 @@
       <c r="Y203" s="2"/>
       <c r="Z203" s="2"/>
     </row>
-    <row r="204" ht="51.75" spans="1:26">
-      <c r="A204" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>125</v>
-      </c>
+    <row r="204" ht="17.55" spans="1:26">
+      <c r="A204" s="2"/>
+      <c r="B204" s="2"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
@@ -10072,13 +10010,9 @@
       <c r="Y204" s="2"/>
       <c r="Z204" s="2"/>
     </row>
-    <row r="205" ht="51.75" spans="1:26">
-      <c r="A205" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>125</v>
-      </c>
+    <row r="205" ht="17.55" spans="1:26">
+      <c r="A205" s="2"/>
+      <c r="B205" s="2"/>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
@@ -10104,13 +10038,9 @@
       <c r="Y205" s="2"/>
       <c r="Z205" s="2"/>
     </row>
-    <row r="206" ht="51.75" spans="1:26">
-      <c r="A206" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>125</v>
-      </c>
+    <row r="206" ht="17.55" spans="1:26">
+      <c r="A206" s="2"/>
+      <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
@@ -10136,13 +10066,9 @@
       <c r="Y206" s="2"/>
       <c r="Z206" s="2"/>
     </row>
-    <row r="207" ht="51.75" spans="1:26">
-      <c r="A207" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>133</v>
-      </c>
+    <row r="207" ht="17.55" spans="1:26">
+      <c r="A207" s="2"/>
+      <c r="B207" s="2"/>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
@@ -10168,13 +10094,9 @@
       <c r="Y207" s="2"/>
       <c r="Z207" s="2"/>
     </row>
-    <row r="208" ht="51.75" spans="1:26">
-      <c r="A208" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>133</v>
-      </c>
+    <row r="208" ht="17.55" spans="1:26">
+      <c r="A208" s="2"/>
+      <c r="B208" s="2"/>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
@@ -10200,13 +10122,9 @@
       <c r="Y208" s="2"/>
       <c r="Z208" s="2"/>
     </row>
-    <row r="209" ht="34.75" spans="1:26">
-      <c r="A209" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>128</v>
-      </c>
+    <row r="209" ht="17.55" spans="1:26">
+      <c r="A209" s="2"/>
+      <c r="B209" s="2"/>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
@@ -10232,13 +10150,9 @@
       <c r="Y209" s="2"/>
       <c r="Z209" s="2"/>
     </row>
-    <row r="210" ht="34.75" spans="1:26">
-      <c r="A210" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>128</v>
-      </c>
+    <row r="210" ht="17.55" spans="1:26">
+      <c r="A210" s="2"/>
+      <c r="B210" s="2"/>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
@@ -10264,13 +10178,9 @@
       <c r="Y210" s="2"/>
       <c r="Z210" s="2"/>
     </row>
-    <row r="211" ht="34.75" spans="1:26">
-      <c r="A211" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>129</v>
-      </c>
+    <row r="211" ht="17.55" spans="1:26">
+      <c r="A211" s="2"/>
+      <c r="B211" s="2"/>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
@@ -10296,13 +10206,9 @@
       <c r="Y211" s="2"/>
       <c r="Z211" s="2"/>
     </row>
-    <row r="212" ht="34.75" spans="1:26">
-      <c r="A212" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>129</v>
-      </c>
+    <row r="212" ht="17.55" spans="1:26">
+      <c r="A212" s="2"/>
+      <c r="B212" s="2"/>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
@@ -10328,13 +10234,9 @@
       <c r="Y212" s="2"/>
       <c r="Z212" s="2"/>
     </row>
-    <row r="213" ht="34.75" spans="1:26">
-      <c r="A213" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>129</v>
-      </c>
+    <row r="213" ht="17.55" spans="1:26">
+      <c r="A213" s="2"/>
+      <c r="B213" s="2"/>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
@@ -10360,13 +10262,9 @@
       <c r="Y213" s="2"/>
       <c r="Z213" s="2"/>
     </row>
-    <row r="214" ht="34.75" spans="1:26">
-      <c r="A214" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>129</v>
-      </c>
+    <row r="214" ht="17.55" spans="1:26">
+      <c r="A214" s="2"/>
+      <c r="B214" s="2"/>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
@@ -10392,13 +10290,9 @@
       <c r="Y214" s="2"/>
       <c r="Z214" s="2"/>
     </row>
-    <row r="215" ht="34.75" spans="1:26">
-      <c r="A215" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>129</v>
-      </c>
+    <row r="215" ht="17.55" spans="1:26">
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
@@ -10424,13 +10318,9 @@
       <c r="Y215" s="2"/>
       <c r="Z215" s="2"/>
     </row>
-    <row r="216" ht="68.75" spans="1:26">
-      <c r="A216" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>131</v>
-      </c>
+    <row r="216" ht="17.55" spans="1:26">
+      <c r="A216" s="2"/>
+      <c r="B216" s="2"/>
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
@@ -10456,13 +10346,9 @@
       <c r="Y216" s="2"/>
       <c r="Z216" s="2"/>
     </row>
-    <row r="217" ht="51.75" spans="1:26">
-      <c r="A217" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>132</v>
-      </c>
+    <row r="217" ht="17.55" spans="1:26">
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
@@ -10488,13 +10374,9 @@
       <c r="Y217" s="2"/>
       <c r="Z217" s="2"/>
     </row>
-    <row r="218" ht="68.75" spans="1:26">
-      <c r="A218" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>134</v>
-      </c>
+    <row r="218" ht="17.55" spans="1:26">
+      <c r="A218" s="2"/>
+      <c r="B218" s="2"/>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
@@ -10520,13 +10402,9 @@
       <c r="Y218" s="2"/>
       <c r="Z218" s="2"/>
     </row>
-    <row r="219" ht="34.75" spans="1:26">
-      <c r="A219" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>135</v>
-      </c>
+    <row r="219" ht="17.55" spans="1:26">
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
@@ -10552,13 +10430,9 @@
       <c r="Y219" s="2"/>
       <c r="Z219" s="2"/>
     </row>
-    <row r="220" ht="17.75" spans="1:26">
-      <c r="A220" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>136</v>
-      </c>
+    <row r="220" ht="17.55" spans="1:26">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
@@ -10584,13 +10458,9 @@
       <c r="Y220" s="2"/>
       <c r="Z220" s="2"/>
     </row>
-    <row r="221" ht="17.75" spans="1:26">
-      <c r="A221" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>136</v>
-      </c>
+    <row r="221" ht="17.55" spans="1:26">
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
@@ -10616,13 +10486,9 @@
       <c r="Y221" s="2"/>
       <c r="Z221" s="2"/>
     </row>
-    <row r="222" ht="17.75" spans="1:26">
-      <c r="A222" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>136</v>
-      </c>
+    <row r="222" ht="17.55" spans="1:26">
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
@@ -10648,13 +10514,9 @@
       <c r="Y222" s="2"/>
       <c r="Z222" s="2"/>
     </row>
-    <row r="223" ht="17.75" spans="1:26">
-      <c r="A223" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>136</v>
-      </c>
+    <row r="223" ht="17.55" spans="1:26">
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
       <c r="C223" s="2"/>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
@@ -10680,13 +10542,9 @@
       <c r="Y223" s="2"/>
       <c r="Z223" s="2"/>
     </row>
-    <row r="224" ht="17.75" spans="1:26">
-      <c r="A224" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>136</v>
-      </c>
+    <row r="224" ht="17.55" spans="1:26">
+      <c r="A224" s="2"/>
+      <c r="B224" s="2"/>
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
@@ -10712,13 +10570,9 @@
       <c r="Y224" s="2"/>
       <c r="Z224" s="2"/>
     </row>
-    <row r="225" ht="51.75" spans="1:26">
-      <c r="A225" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>142</v>
-      </c>
+    <row r="225" ht="17.55" spans="1:26">
+      <c r="A225" s="2"/>
+      <c r="B225" s="2"/>
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
@@ -10744,13 +10598,9 @@
       <c r="Y225" s="2"/>
       <c r="Z225" s="2"/>
     </row>
-    <row r="226" ht="51.75" spans="1:26">
-      <c r="A226" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>142</v>
-      </c>
+    <row r="226" ht="17.55" spans="1:26">
+      <c r="A226" s="2"/>
+      <c r="B226" s="2"/>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
@@ -10776,13 +10626,9 @@
       <c r="Y226" s="2"/>
       <c r="Z226" s="2"/>
     </row>
-    <row r="227" ht="51.75" spans="1:26">
-      <c r="A227" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>142</v>
-      </c>
+    <row r="227" ht="17.55" spans="1:26">
+      <c r="A227" s="2"/>
+      <c r="B227" s="2"/>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
@@ -10808,13 +10654,9 @@
       <c r="Y227" s="2"/>
       <c r="Z227" s="2"/>
     </row>
-    <row r="228" ht="51.75" spans="1:26">
-      <c r="A228" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>142</v>
-      </c>
+    <row r="228" ht="17.55" spans="1:26">
+      <c r="A228" s="2"/>
+      <c r="B228" s="2"/>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
@@ -10840,13 +10682,9 @@
       <c r="Y228" s="2"/>
       <c r="Z228" s="2"/>
     </row>
-    <row r="229" ht="51.75" spans="1:26">
-      <c r="A229" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>142</v>
-      </c>
+    <row r="229" ht="17.55" spans="1:26">
+      <c r="A229" s="2"/>
+      <c r="B229" s="2"/>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
@@ -10872,13 +10710,9 @@
       <c r="Y229" s="2"/>
       <c r="Z229" s="2"/>
     </row>
-    <row r="230" ht="34.75" spans="1:26">
-      <c r="A230" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>144</v>
-      </c>
+    <row r="230" ht="17.55" spans="1:26">
+      <c r="A230" s="2"/>
+      <c r="B230" s="2"/>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
@@ -10904,13 +10738,9 @@
       <c r="Y230" s="2"/>
       <c r="Z230" s="2"/>
     </row>
-    <row r="231" ht="34.75" spans="1:26">
-      <c r="A231" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>144</v>
-      </c>
+    <row r="231" ht="17.55" spans="1:26">
+      <c r="A231" s="2"/>
+      <c r="B231" s="2"/>
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
@@ -10936,13 +10766,9 @@
       <c r="Y231" s="2"/>
       <c r="Z231" s="2"/>
     </row>
-    <row r="232" ht="34.75" spans="1:26">
-      <c r="A232" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>144</v>
-      </c>
+    <row r="232" ht="17.55" spans="1:26">
+      <c r="A232" s="2"/>
+      <c r="B232" s="2"/>
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
@@ -10968,13 +10794,9 @@
       <c r="Y232" s="2"/>
       <c r="Z232" s="2"/>
     </row>
-    <row r="233" ht="34.75" spans="1:26">
-      <c r="A233" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>144</v>
-      </c>
+    <row r="233" ht="17.55" spans="1:26">
+      <c r="A233" s="2"/>
+      <c r="B233" s="2"/>
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
@@ -11000,13 +10822,9 @@
       <c r="Y233" s="2"/>
       <c r="Z233" s="2"/>
     </row>
-    <row r="234" ht="34.75" spans="1:26">
-      <c r="A234" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>144</v>
-      </c>
+    <row r="234" ht="17.55" spans="1:26">
+      <c r="A234" s="2"/>
+      <c r="B234" s="2"/>
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
@@ -11032,13 +10850,9 @@
       <c r="Y234" s="2"/>
       <c r="Z234" s="2"/>
     </row>
-    <row r="235" ht="51.75" spans="1:26">
-      <c r="A235" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>138</v>
-      </c>
+    <row r="235" ht="17.55" spans="1:26">
+      <c r="A235" s="2"/>
+      <c r="B235" s="2"/>
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
@@ -11064,13 +10878,9 @@
       <c r="Y235" s="2"/>
       <c r="Z235" s="2"/>
     </row>
-    <row r="236" ht="68.75" spans="1:26">
-      <c r="A236" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>139</v>
-      </c>
+    <row r="236" ht="17.55" spans="1:26">
+      <c r="A236" s="2"/>
+      <c r="B236" s="2"/>
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
@@ -11096,13 +10906,9 @@
       <c r="Y236" s="2"/>
       <c r="Z236" s="2"/>
     </row>
-    <row r="237" ht="51.75" spans="1:26">
-      <c r="A237" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>140</v>
-      </c>
+    <row r="237" ht="17.55" spans="1:26">
+      <c r="A237" s="2"/>
+      <c r="B237" s="2"/>
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
@@ -11128,13 +10934,9 @@
       <c r="Y237" s="2"/>
       <c r="Z237" s="2"/>
     </row>
-    <row r="238" ht="51.75" spans="1:26">
-      <c r="A238" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>140</v>
-      </c>
+    <row r="238" ht="17.55" spans="1:26">
+      <c r="A238" s="2"/>
+      <c r="B238" s="2"/>
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
@@ -11160,13 +10962,9 @@
       <c r="Y238" s="2"/>
       <c r="Z238" s="2"/>
     </row>
-    <row r="239" ht="51.75" spans="1:26">
-      <c r="A239" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>140</v>
-      </c>
+    <row r="239" ht="17.55" spans="1:26">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
@@ -11192,13 +10990,9 @@
       <c r="Y239" s="2"/>
       <c r="Z239" s="2"/>
     </row>
-    <row r="240" ht="68.75" spans="1:26">
-      <c r="A240" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>140</v>
-      </c>
+    <row r="240" ht="17.55" spans="1:26">
+      <c r="A240" s="2"/>
+      <c r="B240" s="2"/>
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
@@ -11224,13 +11018,9 @@
       <c r="Y240" s="2"/>
       <c r="Z240" s="2"/>
     </row>
-    <row r="241" ht="68.75" spans="1:26">
-      <c r="A241" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>140</v>
-      </c>
+    <row r="241" ht="17.55" spans="1:26">
+      <c r="A241" s="2"/>
+      <c r="B241" s="2"/>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
       <c r="E241" s="2"/>
@@ -11256,13 +11046,9 @@
       <c r="Y241" s="2"/>
       <c r="Z241" s="2"/>
     </row>
-    <row r="242" ht="68.75" spans="1:26">
-      <c r="A242" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>140</v>
-      </c>
+    <row r="242" ht="17.55" spans="1:26">
+      <c r="A242" s="2"/>
+      <c r="B242" s="2"/>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
       <c r="E242" s="2"/>
@@ -11288,13 +11074,9 @@
       <c r="Y242" s="2"/>
       <c r="Z242" s="2"/>
     </row>
-    <row r="243" ht="51.75" spans="1:26">
-      <c r="A243" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="243" ht="17.55" spans="1:26">
+      <c r="A243" s="2"/>
+      <c r="B243" s="2"/>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
       <c r="E243" s="2"/>
@@ -11320,13 +11102,9 @@
       <c r="Y243" s="2"/>
       <c r="Z243" s="2"/>
     </row>
-    <row r="244" ht="51.75" spans="1:26">
-      <c r="A244" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="244" ht="17.55" spans="1:26">
+      <c r="A244" s="2"/>
+      <c r="B244" s="2"/>
       <c r="C244" s="2"/>
       <c r="D244" s="2"/>
       <c r="E244" s="2"/>
@@ -11352,13 +11130,9 @@
       <c r="Y244" s="2"/>
       <c r="Z244" s="2"/>
     </row>
-    <row r="245" ht="51.75" spans="1:26">
-      <c r="A245" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="245" ht="17.55" spans="1:26">
+      <c r="A245" s="2"/>
+      <c r="B245" s="2"/>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
       <c r="E245" s="2"/>
@@ -11384,13 +11158,9 @@
       <c r="Y245" s="2"/>
       <c r="Z245" s="2"/>
     </row>
-    <row r="246" ht="68.75" spans="1:26">
-      <c r="A246" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="246" ht="17.55" spans="1:26">
+      <c r="A246" s="2"/>
+      <c r="B246" s="2"/>
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
       <c r="E246" s="2"/>
@@ -11416,13 +11186,9 @@
       <c r="Y246" s="2"/>
       <c r="Z246" s="2"/>
     </row>
-    <row r="247" ht="68.75" spans="1:26">
-      <c r="A247" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="247" ht="17.55" spans="1:26">
+      <c r="A247" s="2"/>
+      <c r="B247" s="2"/>
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
@@ -11448,13 +11214,9 @@
       <c r="Y247" s="2"/>
       <c r="Z247" s="2"/>
     </row>
-    <row r="248" ht="68.75" spans="1:26">
-      <c r="A248" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="248" ht="17.55" spans="1:26">
+      <c r="A248" s="2"/>
+      <c r="B248" s="2"/>
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
@@ -11480,13 +11242,9 @@
       <c r="Y248" s="2"/>
       <c r="Z248" s="2"/>
     </row>
-    <row r="249" ht="51.75" spans="1:26">
-      <c r="A249" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>143</v>
-      </c>
+    <row r="249" ht="17.55" spans="1:26">
+      <c r="A249" s="2"/>
+      <c r="B249" s="2"/>
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
       <c r="E249" s="2"/>
@@ -11512,13 +11270,9 @@
       <c r="Y249" s="2"/>
       <c r="Z249" s="2"/>
     </row>
-    <row r="250" ht="51.75" spans="1:26">
-      <c r="A250" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>143</v>
-      </c>
+    <row r="250" ht="17.55" spans="1:26">
+      <c r="A250" s="2"/>
+      <c r="B250" s="2"/>
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
       <c r="E250" s="2"/>
@@ -11544,13 +11298,9 @@
       <c r="Y250" s="2"/>
       <c r="Z250" s="2"/>
     </row>
-    <row r="251" ht="34.75" spans="1:26">
-      <c r="A251" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>145</v>
-      </c>
+    <row r="251" ht="17.55" spans="1:26">
+      <c r="A251" s="2"/>
+      <c r="B251" s="2"/>
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
       <c r="E251" s="2"/>
@@ -11576,13 +11326,9 @@
       <c r="Y251" s="2"/>
       <c r="Z251" s="2"/>
     </row>
-    <row r="252" ht="34.75" spans="1:26">
-      <c r="A252" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>145</v>
-      </c>
+    <row r="252" ht="17.55" spans="1:26">
+      <c r="A252" s="2"/>
+      <c r="B252" s="2"/>
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
       <c r="E252" s="2"/>
@@ -11608,13 +11354,9 @@
       <c r="Y252" s="2"/>
       <c r="Z252" s="2"/>
     </row>
-    <row r="253" ht="34.75" spans="1:26">
-      <c r="A253" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>145</v>
-      </c>
+    <row r="253" ht="17.55" spans="1:26">
+      <c r="A253" s="2"/>
+      <c r="B253" s="2"/>
       <c r="C253" s="2"/>
       <c r="D253" s="2"/>
       <c r="E253" s="2"/>
@@ -11640,13 +11382,9 @@
       <c r="Y253" s="2"/>
       <c r="Z253" s="2"/>
     </row>
-    <row r="254" ht="34.75" spans="1:26">
-      <c r="A254" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>145</v>
-      </c>
+    <row r="254" ht="17.55" spans="1:26">
+      <c r="A254" s="2"/>
+      <c r="B254" s="2"/>
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
       <c r="E254" s="2"/>
@@ -11672,13 +11410,9 @@
       <c r="Y254" s="2"/>
       <c r="Z254" s="2"/>
     </row>
-    <row r="255" ht="34.75" spans="1:26">
-      <c r="A255" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>145</v>
-      </c>
+    <row r="255" ht="17.55" spans="1:26">
+      <c r="A255" s="2"/>
+      <c r="B255" s="2"/>
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
       <c r="E255" s="2"/>
@@ -11704,13 +11438,9 @@
       <c r="Y255" s="2"/>
       <c r="Z255" s="2"/>
     </row>
-    <row r="256" ht="34.75" spans="1:26">
-      <c r="A256" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>145</v>
-      </c>
+    <row r="256" ht="17.55" spans="1:26">
+      <c r="A256" s="2"/>
+      <c r="B256" s="2"/>
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
       <c r="E256" s="2"/>
@@ -11736,13 +11466,9 @@
       <c r="Y256" s="2"/>
       <c r="Z256" s="2"/>
     </row>
-    <row r="257" ht="34.75" spans="1:26">
-      <c r="A257" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>145</v>
-      </c>
+    <row r="257" ht="17.55" spans="1:26">
+      <c r="A257" s="2"/>
+      <c r="B257" s="2"/>
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
       <c r="E257" s="2"/>
@@ -11768,13 +11494,9 @@
       <c r="Y257" s="2"/>
       <c r="Z257" s="2"/>
     </row>
-    <row r="258" ht="17.75" spans="1:26">
-      <c r="A258" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B258" s="1" t="s">
-        <v>146</v>
-      </c>
+    <row r="258" ht="17.55" spans="1:26">
+      <c r="A258" s="2"/>
+      <c r="B258" s="2"/>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
       <c r="E258" s="2"/>
@@ -11800,13 +11522,9 @@
       <c r="Y258" s="2"/>
       <c r="Z258" s="2"/>
     </row>
-    <row r="259" ht="34.75" spans="1:26">
-      <c r="A259" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>147</v>
-      </c>
+    <row r="259" ht="17.55" spans="1:26">
+      <c r="A259" s="2"/>
+      <c r="B259" s="2"/>
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
       <c r="E259" s="2"/>
@@ -11832,13 +11550,9 @@
       <c r="Y259" s="2"/>
       <c r="Z259" s="2"/>
     </row>
-    <row r="260" ht="34.75" spans="1:26">
-      <c r="A260" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>147</v>
-      </c>
+    <row r="260" ht="17.55" spans="1:26">
+      <c r="A260" s="2"/>
+      <c r="B260" s="2"/>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
       <c r="E260" s="2"/>
@@ -11864,13 +11578,9 @@
       <c r="Y260" s="2"/>
       <c r="Z260" s="2"/>
     </row>
-    <row r="261" ht="51.75" spans="1:26">
-      <c r="A261" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>148</v>
-      </c>
+    <row r="261" ht="17.55" spans="1:26">
+      <c r="A261" s="2"/>
+      <c r="B261" s="2"/>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
       <c r="E261" s="2"/>
@@ -11896,13 +11606,9 @@
       <c r="Y261" s="2"/>
       <c r="Z261" s="2"/>
     </row>
-    <row r="262" ht="34.75" spans="1:26">
-      <c r="A262" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>149</v>
-      </c>
+    <row r="262" ht="17.55" spans="1:26">
+      <c r="A262" s="2"/>
+      <c r="B262" s="2"/>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
       <c r="E262" s="2"/>
@@ -11928,13 +11634,9 @@
       <c r="Y262" s="2"/>
       <c r="Z262" s="2"/>
     </row>
-    <row r="263" ht="34.75" spans="1:26">
-      <c r="A263" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>149</v>
-      </c>
+    <row r="263" ht="17.55" spans="1:26">
+      <c r="A263" s="2"/>
+      <c r="B263" s="2"/>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
       <c r="E263" s="2"/>
@@ -11960,13 +11662,9 @@
       <c r="Y263" s="2"/>
       <c r="Z263" s="2"/>
     </row>
-    <row r="264" ht="34.75" spans="1:26">
-      <c r="A264" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>149</v>
-      </c>
+    <row r="264" ht="17.55" spans="1:26">
+      <c r="A264" s="2"/>
+      <c r="B264" s="2"/>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
       <c r="E264" s="2"/>
@@ -11992,13 +11690,9 @@
       <c r="Y264" s="2"/>
       <c r="Z264" s="2"/>
     </row>
-    <row r="265" ht="51.75" spans="1:26">
-      <c r="A265" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B265" s="1" t="s">
-        <v>149</v>
-      </c>
+    <row r="265" ht="17.55" spans="1:26">
+      <c r="A265" s="2"/>
+      <c r="B265" s="2"/>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
       <c r="E265" s="2"/>
@@ -12024,13 +11718,9 @@
       <c r="Y265" s="2"/>
       <c r="Z265" s="2"/>
     </row>
-    <row r="266" ht="51.75" spans="1:26">
-      <c r="A266" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>149</v>
-      </c>
+    <row r="266" ht="17.55" spans="1:26">
+      <c r="A266" s="2"/>
+      <c r="B266" s="2"/>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
       <c r="E266" s="2"/>
@@ -12056,13 +11746,9 @@
       <c r="Y266" s="2"/>
       <c r="Z266" s="2"/>
     </row>
-    <row r="267" ht="51.75" spans="1:26">
-      <c r="A267" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>149</v>
-      </c>
+    <row r="267" ht="17.55" spans="1:26">
+      <c r="A267" s="2"/>
+      <c r="B267" s="2"/>
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
@@ -12088,13 +11774,9 @@
       <c r="Y267" s="2"/>
       <c r="Z267" s="2"/>
     </row>
-    <row r="268" ht="51.75" spans="1:26">
-      <c r="A268" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="268" ht="17.55" spans="1:26">
+      <c r="A268" s="2"/>
+      <c r="B268" s="2"/>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
       <c r="E268" s="2"/>
@@ -12120,13 +11802,9 @@
       <c r="Y268" s="2"/>
       <c r="Z268" s="2"/>
     </row>
-    <row r="269" ht="51.75" spans="1:26">
-      <c r="A269" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="269" ht="17.55" spans="1:26">
+      <c r="A269" s="2"/>
+      <c r="B269" s="2"/>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
       <c r="E269" s="2"/>
@@ -12152,13 +11830,9 @@
       <c r="Y269" s="2"/>
       <c r="Z269" s="2"/>
     </row>
-    <row r="270" ht="51.75" spans="1:26">
-      <c r="A270" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="270" ht="17.55" spans="1:26">
+      <c r="A270" s="2"/>
+      <c r="B270" s="2"/>
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
       <c r="E270" s="2"/>
@@ -12184,13 +11858,9 @@
       <c r="Y270" s="2"/>
       <c r="Z270" s="2"/>
     </row>
-    <row r="271" ht="68.75" spans="1:26">
-      <c r="A271" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B271" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="271" ht="17.55" spans="1:26">
+      <c r="A271" s="2"/>
+      <c r="B271" s="2"/>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
       <c r="E271" s="2"/>
@@ -12216,13 +11886,9 @@
       <c r="Y271" s="2"/>
       <c r="Z271" s="2"/>
     </row>
-    <row r="272" ht="68.75" spans="1:26">
-      <c r="A272" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="272" ht="17.55" spans="1:26">
+      <c r="A272" s="2"/>
+      <c r="B272" s="2"/>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
       <c r="E272" s="2"/>
@@ -12248,13 +11914,9 @@
       <c r="Y272" s="2"/>
       <c r="Z272" s="2"/>
     </row>
-    <row r="273" ht="34.75" spans="1:26">
-      <c r="A273" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>150</v>
-      </c>
+    <row r="273" ht="17.55" spans="1:26">
+      <c r="A273" s="2"/>
+      <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
       <c r="E273" s="2"/>
@@ -12280,13 +11942,9 @@
       <c r="Y273" s="2"/>
       <c r="Z273" s="2"/>
     </row>
-    <row r="274" ht="34.75" spans="1:26">
-      <c r="A274" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B274" s="1" t="s">
-        <v>150</v>
-      </c>
+    <row r="274" ht="17.55" spans="1:26">
+      <c r="A274" s="2"/>
+      <c r="B274" s="2"/>
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
       <c r="E274" s="2"/>
@@ -12312,13 +11970,9 @@
       <c r="Y274" s="2"/>
       <c r="Z274" s="2"/>
     </row>
-    <row r="275" ht="34.75" spans="1:26">
-      <c r="A275" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B275" s="1" t="s">
-        <v>150</v>
-      </c>
+    <row r="275" ht="17.55" spans="1:26">
+      <c r="A275" s="2"/>
+      <c r="B275" s="2"/>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
       <c r="E275" s="2"/>
@@ -12344,13 +11998,9 @@
       <c r="Y275" s="2"/>
       <c r="Z275" s="2"/>
     </row>
-    <row r="276" ht="34.75" spans="1:26">
-      <c r="A276" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>150</v>
-      </c>
+    <row r="276" ht="17.55" spans="1:26">
+      <c r="A276" s="2"/>
+      <c r="B276" s="2"/>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
       <c r="E276" s="2"/>
@@ -12376,13 +12026,9 @@
       <c r="Y276" s="2"/>
       <c r="Z276" s="2"/>
     </row>
-    <row r="277" ht="34.75" spans="1:26">
-      <c r="A277" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B277" s="1" t="s">
-        <v>150</v>
-      </c>
+    <row r="277" ht="17.55" spans="1:26">
+      <c r="A277" s="2"/>
+      <c r="B277" s="2"/>
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
       <c r="E277" s="2"/>
@@ -12408,13 +12054,9 @@
       <c r="Y277" s="2"/>
       <c r="Z277" s="2"/>
     </row>
-    <row r="278" ht="34.75" spans="1:26">
-      <c r="A278" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B278" s="1" t="s">
-        <v>151</v>
-      </c>
+    <row r="278" ht="17.55" spans="1:26">
+      <c r="A278" s="2"/>
+      <c r="B278" s="2"/>
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
@@ -12440,13 +12082,9 @@
       <c r="Y278" s="2"/>
       <c r="Z278" s="2"/>
     </row>
-    <row r="279" ht="34.75" spans="1:26">
-      <c r="A279" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>151</v>
-      </c>
+    <row r="279" ht="17.55" spans="1:26">
+      <c r="A279" s="2"/>
+      <c r="B279" s="2"/>
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
       <c r="E279" s="2"/>
@@ -12472,13 +12110,9 @@
       <c r="Y279" s="2"/>
       <c r="Z279" s="2"/>
     </row>
-    <row r="280" ht="68.75" spans="1:26">
-      <c r="A280" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B280" s="3" t="s">
-        <v>43</v>
-      </c>
+    <row r="280" ht="17.55" spans="1:26">
+      <c r="A280" s="2"/>
+      <c r="B280" s="2"/>
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
       <c r="E280" s="2"/>
@@ -12504,13 +12138,9 @@
       <c r="Y280" s="2"/>
       <c r="Z280" s="2"/>
     </row>
-    <row r="281" ht="84.75" spans="1:26">
-      <c r="A281" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B281" s="3" t="s">
-        <v>42</v>
-      </c>
+    <row r="281" ht="17.55" spans="1:26">
+      <c r="A281" s="2"/>
+      <c r="B281" s="2"/>
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
       <c r="E281" s="2"/>
@@ -12536,13 +12166,9 @@
       <c r="Y281" s="2"/>
       <c r="Z281" s="2"/>
     </row>
-    <row r="282" ht="68.75" spans="1:26">
-      <c r="A282" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>152</v>
-      </c>
+    <row r="282" ht="17.55" spans="1:26">
+      <c r="A282" s="2"/>
+      <c r="B282" s="2"/>
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
       <c r="E282" s="2"/>
@@ -12568,13 +12194,9 @@
       <c r="Y282" s="2"/>
       <c r="Z282" s="2"/>
     </row>
-    <row r="283" ht="34.75" spans="1:26">
-      <c r="A283" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B283" s="1" t="s">
-        <v>153</v>
-      </c>
+    <row r="283" ht="17.55" spans="1:26">
+      <c r="A283" s="2"/>
+      <c r="B283" s="2"/>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
       <c r="E283" s="2"/>
@@ -12600,13 +12222,9 @@
       <c r="Y283" s="2"/>
       <c r="Z283" s="2"/>
     </row>
-    <row r="284" ht="34.75" spans="1:26">
-      <c r="A284" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B284" s="1" t="s">
-        <v>153</v>
-      </c>
+    <row r="284" ht="17.55" spans="1:26">
+      <c r="A284" s="2"/>
+      <c r="B284" s="2"/>
       <c r="C284" s="2"/>
       <c r="D284" s="2"/>
       <c r="E284" s="2"/>
@@ -12632,13 +12250,9 @@
       <c r="Y284" s="2"/>
       <c r="Z284" s="2"/>
     </row>
-    <row r="285" ht="34.75" spans="1:26">
-      <c r="A285" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B285" s="1" t="s">
-        <v>153</v>
-      </c>
+    <row r="285" ht="17.55" spans="1:26">
+      <c r="A285" s="2"/>
+      <c r="B285" s="2"/>
       <c r="C285" s="2"/>
       <c r="D285" s="2"/>
       <c r="E285" s="2"/>
@@ -12664,13 +12278,9 @@
       <c r="Y285" s="2"/>
       <c r="Z285" s="2"/>
     </row>
-    <row r="286" ht="34.75" spans="1:26">
-      <c r="A286" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>154</v>
-      </c>
+    <row r="286" ht="17.55" spans="1:26">
+      <c r="A286" s="2"/>
+      <c r="B286" s="2"/>
       <c r="C286" s="2"/>
       <c r="D286" s="2"/>
       <c r="E286" s="2"/>
@@ -12696,13 +12306,9 @@
       <c r="Y286" s="2"/>
       <c r="Z286" s="2"/>
     </row>
-    <row r="287" ht="34.75" spans="1:26">
-      <c r="A287" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B287" s="1" t="s">
-        <v>154</v>
-      </c>
+    <row r="287" ht="17.55" spans="1:26">
+      <c r="A287" s="2"/>
+      <c r="B287" s="2"/>
       <c r="C287" s="2"/>
       <c r="D287" s="2"/>
       <c r="E287" s="2"/>
@@ -12728,13 +12334,9 @@
       <c r="Y287" s="2"/>
       <c r="Z287" s="2"/>
     </row>
-    <row r="288" ht="34.75" spans="1:26">
-      <c r="A288" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B288" s="1" t="s">
-        <v>154</v>
-      </c>
+    <row r="288" ht="17.55" spans="1:26">
+      <c r="A288" s="2"/>
+      <c r="B288" s="2"/>
       <c r="C288" s="2"/>
       <c r="D288" s="2"/>
       <c r="E288" s="2"/>
@@ -12760,13 +12362,9 @@
       <c r="Y288" s="2"/>
       <c r="Z288" s="2"/>
     </row>
-    <row r="289" ht="34.75" spans="1:26">
-      <c r="A289" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B289" s="1" t="s">
-        <v>154</v>
-      </c>
+    <row r="289" ht="17.55" spans="1:26">
+      <c r="A289" s="2"/>
+      <c r="B289" s="2"/>
       <c r="C289" s="2"/>
       <c r="D289" s="2"/>
       <c r="E289" s="2"/>
@@ -12792,13 +12390,9 @@
       <c r="Y289" s="2"/>
       <c r="Z289" s="2"/>
     </row>
-    <row r="290" ht="34.75" spans="1:26">
-      <c r="A290" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B290" s="1" t="s">
-        <v>154</v>
-      </c>
+    <row r="290" ht="17.55" spans="1:26">
+      <c r="A290" s="2"/>
+      <c r="B290" s="2"/>
       <c r="C290" s="2"/>
       <c r="D290" s="2"/>
       <c r="E290" s="2"/>
@@ -12824,13 +12418,9 @@
       <c r="Y290" s="2"/>
       <c r="Z290" s="2"/>
     </row>
-    <row r="291" ht="34.75" spans="1:26">
-      <c r="A291" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B291" s="1" t="s">
-        <v>155</v>
-      </c>
+    <row r="291" ht="17.55" spans="1:26">
+      <c r="A291" s="2"/>
+      <c r="B291" s="2"/>
       <c r="C291" s="2"/>
       <c r="D291" s="2"/>
       <c r="E291" s="2"/>
@@ -12856,13 +12446,9 @@
       <c r="Y291" s="2"/>
       <c r="Z291" s="2"/>
     </row>
-    <row r="292" ht="34.75" spans="1:26">
-      <c r="A292" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B292" s="1" t="s">
-        <v>155</v>
-      </c>
+    <row r="292" ht="17.55" spans="1:26">
+      <c r="A292" s="2"/>
+      <c r="B292" s="2"/>
       <c r="C292" s="2"/>
       <c r="D292" s="2"/>
       <c r="E292" s="2"/>
@@ -12888,13 +12474,9 @@
       <c r="Y292" s="2"/>
       <c r="Z292" s="2"/>
     </row>
-    <row r="293" ht="34.75" spans="1:26">
-      <c r="A293" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B293" s="1" t="s">
-        <v>155</v>
-      </c>
+    <row r="293" ht="17.55" spans="1:26">
+      <c r="A293" s="2"/>
+      <c r="B293" s="2"/>
       <c r="C293" s="2"/>
       <c r="D293" s="2"/>
       <c r="E293" s="2"/>
@@ -12920,13 +12502,9 @@
       <c r="Y293" s="2"/>
       <c r="Z293" s="2"/>
     </row>
-    <row r="294" ht="34.75" spans="1:26">
-      <c r="A294" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B294" s="1" t="s">
-        <v>157</v>
-      </c>
+    <row r="294" ht="17.55" spans="1:26">
+      <c r="A294" s="2"/>
+      <c r="B294" s="2"/>
       <c r="C294" s="2"/>
       <c r="D294" s="2"/>
       <c r="E294" s="2"/>
@@ -12952,13 +12530,9 @@
       <c r="Y294" s="2"/>
       <c r="Z294" s="2"/>
     </row>
-    <row r="295" ht="34.75" spans="1:26">
-      <c r="A295" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B295" s="1" t="s">
-        <v>157</v>
-      </c>
+    <row r="295" ht="17.55" spans="1:26">
+      <c r="A295" s="2"/>
+      <c r="B295" s="2"/>
       <c r="C295" s="2"/>
       <c r="D295" s="2"/>
       <c r="E295" s="2"/>
@@ -12984,13 +12558,9 @@
       <c r="Y295" s="2"/>
       <c r="Z295" s="2"/>
     </row>
-    <row r="296" ht="34.75" spans="1:26">
-      <c r="A296" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B296" s="1" t="s">
-        <v>157</v>
-      </c>
+    <row r="296" ht="17.55" spans="1:26">
+      <c r="A296" s="2"/>
+      <c r="B296" s="2"/>
       <c r="C296" s="2"/>
       <c r="D296" s="2"/>
       <c r="E296" s="2"/>
@@ -13016,13 +12586,9 @@
       <c r="Y296" s="2"/>
       <c r="Z296" s="2"/>
     </row>
-    <row r="297" ht="34.75" spans="1:26">
-      <c r="A297" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>157</v>
-      </c>
+    <row r="297" ht="17.55" spans="1:26">
+      <c r="A297" s="2"/>
+      <c r="B297" s="2"/>
       <c r="C297" s="2"/>
       <c r="D297" s="2"/>
       <c r="E297" s="2"/>
@@ -13048,13 +12614,9 @@
       <c r="Y297" s="2"/>
       <c r="Z297" s="2"/>
     </row>
-    <row r="298" ht="51.75" spans="1:26">
-      <c r="A298" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B298" s="1" t="s">
-        <v>158</v>
-      </c>
+    <row r="298" ht="17.55" spans="1:26">
+      <c r="A298" s="2"/>
+      <c r="B298" s="2"/>
       <c r="C298" s="2"/>
       <c r="D298" s="2"/>
       <c r="E298" s="2"/>
@@ -13080,13 +12642,9 @@
       <c r="Y298" s="2"/>
       <c r="Z298" s="2"/>
     </row>
-    <row r="299" ht="51.75" spans="1:26">
-      <c r="A299" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>158</v>
-      </c>
+    <row r="299" ht="17.55" spans="1:26">
+      <c r="A299" s="2"/>
+      <c r="B299" s="2"/>
       <c r="C299" s="2"/>
       <c r="D299" s="2"/>
       <c r="E299" s="2"/>
@@ -13112,13 +12670,9 @@
       <c r="Y299" s="2"/>
       <c r="Z299" s="2"/>
     </row>
-    <row r="300" ht="68.75" spans="1:26">
-      <c r="A300" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B300" s="1" t="s">
-        <v>159</v>
-      </c>
+    <row r="300" ht="17.55" spans="1:26">
+      <c r="A300" s="2"/>
+      <c r="B300" s="2"/>
       <c r="C300" s="2"/>
       <c r="D300" s="2"/>
       <c r="E300" s="2"/>
@@ -13144,13 +12698,9 @@
       <c r="Y300" s="2"/>
       <c r="Z300" s="2"/>
     </row>
-    <row r="301" ht="68.75" spans="1:26">
-      <c r="A301" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>160</v>
-      </c>
+    <row r="301" ht="17.55" spans="1:26">
+      <c r="A301" s="2"/>
+      <c r="B301" s="2"/>
       <c r="C301" s="2"/>
       <c r="D301" s="2"/>
       <c r="E301" s="2"/>
@@ -13176,13 +12726,9 @@
       <c r="Y301" s="2"/>
       <c r="Z301" s="2"/>
     </row>
-    <row r="302" ht="68.75" spans="1:26">
-      <c r="A302" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>42</v>
-      </c>
+    <row r="302" ht="17.55" spans="1:26">
+      <c r="A302" s="2"/>
+      <c r="B302" s="2"/>
       <c r="C302" s="2"/>
       <c r="D302" s="2"/>
       <c r="E302" s="2"/>
@@ -13208,13 +12754,9 @@
       <c r="Y302" s="2"/>
       <c r="Z302" s="2"/>
     </row>
-    <row r="303" ht="68.75" spans="1:26">
-      <c r="A303" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>42</v>
-      </c>
+    <row r="303" ht="17.55" spans="1:26">
+      <c r="A303" s="2"/>
+      <c r="B303" s="2"/>
       <c r="C303" s="2"/>
       <c r="D303" s="2"/>
       <c r="E303" s="2"/>
@@ -13240,13 +12782,9 @@
       <c r="Y303" s="2"/>
       <c r="Z303" s="2"/>
     </row>
-    <row r="304" ht="68.75" spans="1:26">
-      <c r="A304" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>42</v>
-      </c>
+    <row r="304" ht="17.55" spans="1:26">
+      <c r="A304" s="2"/>
+      <c r="B304" s="2"/>
       <c r="C304" s="2"/>
       <c r="D304" s="2"/>
       <c r="E304" s="2"/>
@@ -13272,13 +12810,9 @@
       <c r="Y304" s="2"/>
       <c r="Z304" s="2"/>
     </row>
-    <row r="305" ht="84.75" spans="1:26">
-      <c r="A305" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B305" s="1" t="s">
-        <v>42</v>
-      </c>
+    <row r="305" ht="17.55" spans="1:26">
+      <c r="A305" s="2"/>
+      <c r="B305" s="2"/>
       <c r="C305" s="2"/>
       <c r="D305" s="2"/>
       <c r="E305" s="2"/>
@@ -13304,13 +12838,9 @@
       <c r="Y305" s="2"/>
       <c r="Z305" s="2"/>
     </row>
-    <row r="306" ht="84.75" spans="1:26">
-      <c r="A306" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B306" s="1" t="s">
-        <v>42</v>
-      </c>
+    <row r="306" ht="17.55" spans="1:26">
+      <c r="A306" s="2"/>
+      <c r="B306" s="2"/>
       <c r="C306" s="2"/>
       <c r="D306" s="2"/>
       <c r="E306" s="2"/>
@@ -13336,13 +12866,9 @@
       <c r="Y306" s="2"/>
       <c r="Z306" s="2"/>
     </row>
-    <row r="307" ht="84.75" spans="1:26">
-      <c r="A307" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>42</v>
-      </c>
+    <row r="307" ht="17.55" spans="1:26">
+      <c r="A307" s="2"/>
+      <c r="B307" s="2"/>
       <c r="C307" s="2"/>
       <c r="D307" s="2"/>
       <c r="E307" s="2"/>
@@ -13368,13 +12894,9 @@
       <c r="Y307" s="2"/>
       <c r="Z307" s="2"/>
     </row>
-    <row r="308" ht="34.75" spans="1:26">
-      <c r="A308" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>161</v>
-      </c>
+    <row r="308" ht="17.55" spans="1:26">
+      <c r="A308" s="2"/>
+      <c r="B308" s="2"/>
       <c r="C308" s="2"/>
       <c r="D308" s="2"/>
       <c r="E308" s="2"/>
@@ -13400,13 +12922,9 @@
       <c r="Y308" s="2"/>
       <c r="Z308" s="2"/>
     </row>
-    <row r="309" ht="34.75" spans="1:26">
-      <c r="A309" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B309" s="1" t="s">
-        <v>162</v>
-      </c>
+    <row r="309" ht="17.55" spans="1:26">
+      <c r="A309" s="2"/>
+      <c r="B309" s="2"/>
       <c r="C309" s="2"/>
       <c r="D309" s="2"/>
       <c r="E309" s="2"/>
@@ -13432,13 +12950,9 @@
       <c r="Y309" s="2"/>
       <c r="Z309" s="2"/>
     </row>
-    <row r="310" ht="34.75" spans="1:26">
-      <c r="A310" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B310" s="1" t="s">
-        <v>162</v>
-      </c>
+    <row r="310" ht="17.55" spans="1:26">
+      <c r="A310" s="2"/>
+      <c r="B310" s="2"/>
       <c r="C310" s="2"/>
       <c r="D310" s="2"/>
       <c r="E310" s="2"/>
@@ -13464,13 +12978,9 @@
       <c r="Y310" s="2"/>
       <c r="Z310" s="2"/>
     </row>
-    <row r="311" ht="51.75" spans="1:26">
-      <c r="A311" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B311" s="1" t="s">
-        <v>163</v>
-      </c>
+    <row r="311" ht="17.55" spans="1:26">
+      <c r="A311" s="2"/>
+      <c r="B311" s="2"/>
       <c r="C311" s="2"/>
       <c r="D311" s="2"/>
       <c r="E311" s="2"/>
@@ -13496,13 +13006,9 @@
       <c r="Y311" s="2"/>
       <c r="Z311" s="2"/>
     </row>
-    <row r="312" ht="34.75" spans="1:26">
-      <c r="A312" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>171</v>
-      </c>
+    <row r="312" ht="17.55" spans="1:26">
+      <c r="A312" s="2"/>
+      <c r="B312" s="2"/>
       <c r="C312" s="2"/>
       <c r="D312" s="2"/>
       <c r="E312" s="2"/>
@@ -13528,13 +13034,9 @@
       <c r="Y312" s="2"/>
       <c r="Z312" s="2"/>
     </row>
-    <row r="313" ht="34.75" spans="1:26">
-      <c r="A313" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B313" s="1" t="s">
-        <v>171</v>
-      </c>
+    <row r="313" ht="17.55" spans="1:26">
+      <c r="A313" s="2"/>
+      <c r="B313" s="2"/>
       <c r="C313" s="2"/>
       <c r="D313" s="2"/>
       <c r="E313" s="2"/>
@@ -13560,13 +13062,9 @@
       <c r="Y313" s="2"/>
       <c r="Z313" s="2"/>
     </row>
-    <row r="314" ht="34.75" spans="1:26">
-      <c r="A314" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>171</v>
-      </c>
+    <row r="314" ht="17.55" spans="1:26">
+      <c r="A314" s="2"/>
+      <c r="B314" s="2"/>
       <c r="C314" s="2"/>
       <c r="D314" s="2"/>
       <c r="E314" s="2"/>
@@ -13592,13 +13090,9 @@
       <c r="Y314" s="2"/>
       <c r="Z314" s="2"/>
     </row>
-    <row r="315" ht="34.75" spans="1:26">
-      <c r="A315" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>171</v>
-      </c>
+    <row r="315" ht="17.55" spans="1:26">
+      <c r="A315" s="2"/>
+      <c r="B315" s="2"/>
       <c r="C315" s="2"/>
       <c r="D315" s="2"/>
       <c r="E315" s="2"/>
@@ -13624,13 +13118,9 @@
       <c r="Y315" s="2"/>
       <c r="Z315" s="2"/>
     </row>
-    <row r="316" ht="34.75" spans="1:26">
-      <c r="A316" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>173</v>
-      </c>
+    <row r="316" ht="17.55" spans="1:26">
+      <c r="A316" s="2"/>
+      <c r="B316" s="2"/>
       <c r="C316" s="2"/>
       <c r="D316" s="2"/>
       <c r="E316" s="2"/>
@@ -13656,13 +13146,9 @@
       <c r="Y316" s="2"/>
       <c r="Z316" s="2"/>
     </row>
-    <row r="317" ht="34.75" spans="1:26">
-      <c r="A317" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>173</v>
-      </c>
+    <row r="317" ht="17.55" spans="1:26">
+      <c r="A317" s="2"/>
+      <c r="B317" s="2"/>
       <c r="C317" s="2"/>
       <c r="D317" s="2"/>
       <c r="E317" s="2"/>
@@ -13688,13 +13174,9 @@
       <c r="Y317" s="2"/>
       <c r="Z317" s="2"/>
     </row>
-    <row r="318" ht="34.75" spans="1:26">
-      <c r="A318" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>173</v>
-      </c>
+    <row r="318" ht="17.55" spans="1:26">
+      <c r="A318" s="2"/>
+      <c r="B318" s="2"/>
       <c r="C318" s="2"/>
       <c r="D318" s="2"/>
       <c r="E318" s="2"/>
@@ -13720,13 +13202,9 @@
       <c r="Y318" s="2"/>
       <c r="Z318" s="2"/>
     </row>
-    <row r="319" ht="34.75" spans="1:26">
-      <c r="A319" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B319" s="1" t="s">
-        <v>173</v>
-      </c>
+    <row r="319" ht="17.55" spans="1:26">
+      <c r="A319" s="2"/>
+      <c r="B319" s="2"/>
       <c r="C319" s="2"/>
       <c r="D319" s="2"/>
       <c r="E319" s="2"/>
@@ -13752,13 +13230,9 @@
       <c r="Y319" s="2"/>
       <c r="Z319" s="2"/>
     </row>
-    <row r="320" ht="34.75" spans="1:26">
-      <c r="A320" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B320" s="1" t="s">
-        <v>173</v>
-      </c>
+    <row r="320" ht="17.55" spans="1:26">
+      <c r="A320" s="2"/>
+      <c r="B320" s="2"/>
       <c r="C320" s="2"/>
       <c r="D320" s="2"/>
       <c r="E320" s="2"/>
@@ -13784,13 +13258,9 @@
       <c r="Y320" s="2"/>
       <c r="Z320" s="2"/>
     </row>
-    <row r="321" ht="34.75" spans="1:26">
-      <c r="A321" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B321" s="1" t="s">
-        <v>175</v>
-      </c>
+    <row r="321" ht="17.55" spans="1:26">
+      <c r="A321" s="2"/>
+      <c r="B321" s="2"/>
       <c r="C321" s="2"/>
       <c r="D321" s="2"/>
       <c r="E321" s="2"/>
@@ -13816,13 +13286,9 @@
       <c r="Y321" s="2"/>
       <c r="Z321" s="2"/>
     </row>
-    <row r="322" ht="34.75" spans="1:26">
-      <c r="A322" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>175</v>
-      </c>
+    <row r="322" ht="17.55" spans="1:26">
+      <c r="A322" s="2"/>
+      <c r="B322" s="2"/>
       <c r="C322" s="2"/>
       <c r="D322" s="2"/>
       <c r="E322" s="2"/>
@@ -13848,13 +13314,9 @@
       <c r="Y322" s="2"/>
       <c r="Z322" s="2"/>
     </row>
-    <row r="323" ht="34.75" spans="1:26">
-      <c r="A323" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B323" s="1" t="s">
-        <v>165</v>
-      </c>
+    <row r="323" ht="17.55" spans="1:26">
+      <c r="A323" s="2"/>
+      <c r="B323" s="2"/>
       <c r="C323" s="2"/>
       <c r="D323" s="2"/>
       <c r="E323" s="2"/>
@@ -13880,13 +13342,9 @@
       <c r="Y323" s="2"/>
       <c r="Z323" s="2"/>
     </row>
-    <row r="324" ht="51.75" spans="1:26">
-      <c r="A324" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>166</v>
-      </c>
+    <row r="324" ht="17.55" spans="1:26">
+      <c r="A324" s="2"/>
+      <c r="B324" s="2"/>
       <c r="C324" s="2"/>
       <c r="D324" s="2"/>
       <c r="E324" s="2"/>
@@ -13912,13 +13370,9 @@
       <c r="Y324" s="2"/>
       <c r="Z324" s="2"/>
     </row>
-    <row r="325" ht="51.75" spans="1:26">
-      <c r="A325" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B325" s="1" t="s">
-        <v>167</v>
-      </c>
+    <row r="325" ht="17.55" spans="1:26">
+      <c r="A325" s="2"/>
+      <c r="B325" s="2"/>
       <c r="C325" s="2"/>
       <c r="D325" s="2"/>
       <c r="E325" s="2"/>
@@ -13944,13 +13398,9 @@
       <c r="Y325" s="2"/>
       <c r="Z325" s="2"/>
     </row>
-    <row r="326" ht="51.75" spans="1:26">
-      <c r="A326" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B326" s="1" t="s">
-        <v>167</v>
-      </c>
+    <row r="326" ht="17.55" spans="1:26">
+      <c r="A326" s="2"/>
+      <c r="B326" s="2"/>
       <c r="C326" s="2"/>
       <c r="D326" s="2"/>
       <c r="E326" s="2"/>
@@ -13976,13 +13426,9 @@
       <c r="Y326" s="2"/>
       <c r="Z326" s="2"/>
     </row>
-    <row r="327" ht="51.75" spans="1:26">
-      <c r="A327" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B327" s="1" t="s">
-        <v>167</v>
-      </c>
+    <row r="327" ht="17.55" spans="1:26">
+      <c r="A327" s="2"/>
+      <c r="B327" s="2"/>
       <c r="C327" s="2"/>
       <c r="D327" s="2"/>
       <c r="E327" s="2"/>
@@ -14008,13 +13454,9 @@
       <c r="Y327" s="2"/>
       <c r="Z327" s="2"/>
     </row>
-    <row r="328" ht="68.75" spans="1:26">
-      <c r="A328" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>167</v>
-      </c>
+    <row r="328" ht="17.55" spans="1:26">
+      <c r="A328" s="2"/>
+      <c r="B328" s="2"/>
       <c r="C328" s="2"/>
       <c r="D328" s="2"/>
       <c r="E328" s="2"/>
@@ -14040,13 +13482,9 @@
       <c r="Y328" s="2"/>
       <c r="Z328" s="2"/>
     </row>
-    <row r="329" ht="68.75" spans="1:26">
-      <c r="A329" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B329" s="1" t="s">
-        <v>167</v>
-      </c>
+    <row r="329" ht="17.55" spans="1:26">
+      <c r="A329" s="2"/>
+      <c r="B329" s="2"/>
       <c r="C329" s="2"/>
       <c r="D329" s="2"/>
       <c r="E329" s="2"/>
@@ -14072,13 +13510,9 @@
       <c r="Y329" s="2"/>
       <c r="Z329" s="2"/>
     </row>
-    <row r="330" ht="68.75" spans="1:26">
-      <c r="A330" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>167</v>
-      </c>
+    <row r="330" ht="17.55" spans="1:26">
+      <c r="A330" s="2"/>
+      <c r="B330" s="2"/>
       <c r="C330" s="2"/>
       <c r="D330" s="2"/>
       <c r="E330" s="2"/>
@@ -14104,13 +13538,9 @@
       <c r="Y330" s="2"/>
       <c r="Z330" s="2"/>
     </row>
-    <row r="331" ht="51.75" spans="1:26">
-      <c r="A331" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>168</v>
-      </c>
+    <row r="331" ht="17.55" spans="1:26">
+      <c r="A331" s="2"/>
+      <c r="B331" s="2"/>
       <c r="C331" s="2"/>
       <c r="D331" s="2"/>
       <c r="E331" s="2"/>
@@ -14136,13 +13566,9 @@
       <c r="Y331" s="2"/>
       <c r="Z331" s="2"/>
     </row>
-    <row r="332" ht="84.75" spans="1:26">
-      <c r="A332" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>169</v>
-      </c>
+    <row r="332" ht="17.55" spans="1:26">
+      <c r="A332" s="2"/>
+      <c r="B332" s="2"/>
       <c r="C332" s="2"/>
       <c r="D332" s="2"/>
       <c r="E332" s="2"/>
@@ -14168,13 +13594,9 @@
       <c r="Y332" s="2"/>
       <c r="Z332" s="2"/>
     </row>
-    <row r="333" ht="68.75" spans="1:26">
-      <c r="A333" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>170</v>
-      </c>
+    <row r="333" ht="17.55" spans="1:26">
+      <c r="A333" s="2"/>
+      <c r="B333" s="2"/>
       <c r="C333" s="2"/>
       <c r="D333" s="2"/>
       <c r="E333" s="2"/>
@@ -14200,13 +13622,9 @@
       <c r="Y333" s="2"/>
       <c r="Z333" s="2"/>
     </row>
-    <row r="334" ht="84.75" spans="1:26">
-      <c r="A334" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>172</v>
-      </c>
+    <row r="334" ht="17.55" spans="1:26">
+      <c r="A334" s="2"/>
+      <c r="B334" s="2"/>
       <c r="C334" s="2"/>
       <c r="D334" s="2"/>
       <c r="E334" s="2"/>
@@ -14232,13 +13650,9 @@
       <c r="Y334" s="2"/>
       <c r="Z334" s="2"/>
     </row>
-    <row r="335" ht="101.75" spans="1:26">
-      <c r="A335" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B335" s="1" t="s">
-        <v>174</v>
-      </c>
+    <row r="335" ht="17.55" spans="1:26">
+      <c r="A335" s="2"/>
+      <c r="B335" s="2"/>
       <c r="C335" s="2"/>
       <c r="D335" s="2"/>
       <c r="E335" s="2"/>
@@ -14264,13 +13678,9 @@
       <c r="Y335" s="2"/>
       <c r="Z335" s="2"/>
     </row>
-    <row r="336" ht="68.75" spans="1:26">
-      <c r="A336" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B336" s="1" t="s">
-        <v>176</v>
-      </c>
+    <row r="336" ht="17.55" spans="1:26">
+      <c r="A336" s="2"/>
+      <c r="B336" s="2"/>
       <c r="C336" s="2"/>
       <c r="D336" s="2"/>
       <c r="E336" s="2"/>
@@ -14296,13 +13706,9 @@
       <c r="Y336" s="2"/>
       <c r="Z336" s="2"/>
     </row>
-    <row r="337" ht="84.75" spans="1:26">
-      <c r="A337" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B337" s="1" t="s">
-        <v>177</v>
-      </c>
+    <row r="337" ht="17.55" spans="1:26">
+      <c r="A337" s="2"/>
+      <c r="B337" s="2"/>
       <c r="C337" s="2"/>
       <c r="D337" s="2"/>
       <c r="E337" s="2"/>
@@ -14328,13 +13734,9 @@
       <c r="Y337" s="2"/>
       <c r="Z337" s="2"/>
     </row>
-    <row r="338" ht="68.75" spans="1:26">
-      <c r="A338" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B338" s="1" t="s">
-        <v>178</v>
-      </c>
+    <row r="338" ht="17.55" spans="1:26">
+      <c r="A338" s="2"/>
+      <c r="B338" s="2"/>
       <c r="C338" s="2"/>
       <c r="D338" s="2"/>
       <c r="E338" s="2"/>
@@ -14360,13 +13762,9 @@
       <c r="Y338" s="2"/>
       <c r="Z338" s="2"/>
     </row>
-    <row r="339" ht="84.75" spans="1:26">
-      <c r="A339" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B339" s="1" t="s">
-        <v>179</v>
-      </c>
+    <row r="339" ht="17.55" spans="1:26">
+      <c r="A339" s="2"/>
+      <c r="B339" s="2"/>
       <c r="C339" s="2"/>
       <c r="D339" s="2"/>
       <c r="E339" s="2"/>
@@ -14392,13 +13790,9 @@
       <c r="Y339" s="2"/>
       <c r="Z339" s="2"/>
     </row>
-    <row r="340" ht="68.75" spans="1:26">
-      <c r="A340" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B340" s="1" t="s">
-        <v>180</v>
-      </c>
+    <row r="340" ht="17.55" spans="1:26">
+      <c r="A340" s="2"/>
+      <c r="B340" s="2"/>
       <c r="C340" s="2"/>
       <c r="D340" s="2"/>
       <c r="E340" s="2"/>
@@ -14424,13 +13818,9 @@
       <c r="Y340" s="2"/>
       <c r="Z340" s="2"/>
     </row>
-    <row r="341" ht="68.75" spans="1:26">
-      <c r="A341" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B341" s="1" t="s">
-        <v>180</v>
-      </c>
+    <row r="341" ht="17.55" spans="1:26">
+      <c r="A341" s="2"/>
+      <c r="B341" s="2"/>
       <c r="C341" s="2"/>
       <c r="D341" s="2"/>
       <c r="E341" s="2"/>
@@ -14456,13 +13846,9 @@
       <c r="Y341" s="2"/>
       <c r="Z341" s="2"/>
     </row>
-    <row r="342" ht="68.75" spans="1:26">
-      <c r="A342" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B342" s="1" t="s">
-        <v>180</v>
-      </c>
+    <row r="342" ht="17.55" spans="1:26">
+      <c r="A342" s="2"/>
+      <c r="B342" s="2"/>
       <c r="C342" s="2"/>
       <c r="D342" s="2"/>
       <c r="E342" s="2"/>
@@ -14488,13 +13874,9 @@
       <c r="Y342" s="2"/>
       <c r="Z342" s="2"/>
     </row>
-    <row r="343" ht="68.75" spans="1:26">
-      <c r="A343" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B343" s="1" t="s">
-        <v>180</v>
-      </c>
+    <row r="343" ht="17.55" spans="1:26">
+      <c r="A343" s="2"/>
+      <c r="B343" s="2"/>
       <c r="C343" s="2"/>
       <c r="D343" s="2"/>
       <c r="E343" s="2"/>
@@ -14520,13 +13902,9 @@
       <c r="Y343" s="2"/>
       <c r="Z343" s="2"/>
     </row>
-    <row r="344" ht="68.75" spans="1:26">
-      <c r="A344" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B344" s="1" t="s">
-        <v>181</v>
-      </c>
+    <row r="344" ht="17.55" spans="1:26">
+      <c r="A344" s="2"/>
+      <c r="B344" s="2"/>
       <c r="C344" s="2"/>
       <c r="D344" s="2"/>
       <c r="E344" s="2"/>
@@ -14552,13 +13930,9 @@
       <c r="Y344" s="2"/>
       <c r="Z344" s="2"/>
     </row>
-    <row r="345" ht="68.75" spans="1:26">
-      <c r="A345" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B345" s="1" t="s">
-        <v>181</v>
-      </c>
+    <row r="345" ht="17.55" spans="1:26">
+      <c r="A345" s="2"/>
+      <c r="B345" s="2"/>
       <c r="C345" s="2"/>
       <c r="D345" s="2"/>
       <c r="E345" s="2"/>
@@ -14584,13 +13958,9 @@
       <c r="Y345" s="2"/>
       <c r="Z345" s="2"/>
     </row>
-    <row r="346" ht="68.75" spans="1:26">
-      <c r="A346" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B346" s="1" t="s">
-        <v>181</v>
-      </c>
+    <row r="346" ht="17.55" spans="1:26">
+      <c r="A346" s="2"/>
+      <c r="B346" s="2"/>
       <c r="C346" s="2"/>
       <c r="D346" s="2"/>
       <c r="E346" s="2"/>
@@ -14616,13 +13986,9 @@
       <c r="Y346" s="2"/>
       <c r="Z346" s="2"/>
     </row>
-    <row r="347" ht="34.75" spans="1:26">
-      <c r="A347" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B347" s="1" t="s">
-        <v>182</v>
-      </c>
+    <row r="347" ht="17.55" spans="1:26">
+      <c r="A347" s="2"/>
+      <c r="B347" s="2"/>
       <c r="C347" s="2"/>
       <c r="D347" s="2"/>
       <c r="E347" s="2"/>
@@ -14648,13 +14014,9 @@
       <c r="Y347" s="2"/>
       <c r="Z347" s="2"/>
     </row>
-    <row r="348" ht="34.75" spans="1:26">
-      <c r="A348" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B348" s="1" t="s">
-        <v>182</v>
-      </c>
+    <row r="348" ht="17.55" spans="1:26">
+      <c r="A348" s="2"/>
+      <c r="B348" s="2"/>
       <c r="C348" s="2"/>
       <c r="D348" s="2"/>
       <c r="E348" s="2"/>
@@ -14680,13 +14042,9 @@
       <c r="Y348" s="2"/>
       <c r="Z348" s="2"/>
     </row>
-    <row r="349" ht="34.75" spans="1:26">
-      <c r="A349" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B349" s="1" t="s">
-        <v>183</v>
-      </c>
+    <row r="349" ht="17.55" spans="1:26">
+      <c r="A349" s="2"/>
+      <c r="B349" s="2"/>
       <c r="C349" s="2"/>
       <c r="D349" s="2"/>
       <c r="E349" s="2"/>
@@ -14712,13 +14070,9 @@
       <c r="Y349" s="2"/>
       <c r="Z349" s="2"/>
     </row>
-    <row r="350" ht="34.75" spans="1:26">
-      <c r="A350" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B350" s="1" t="s">
-        <v>184</v>
-      </c>
+    <row r="350" ht="17.55" spans="1:26">
+      <c r="A350" s="2"/>
+      <c r="B350" s="2"/>
       <c r="C350" s="2"/>
       <c r="D350" s="2"/>
       <c r="E350" s="2"/>
@@ -14744,13 +14098,9 @@
       <c r="Y350" s="2"/>
       <c r="Z350" s="2"/>
     </row>
-    <row r="351" ht="34.75" spans="1:26">
-      <c r="A351" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B351" s="1" t="s">
-        <v>184</v>
-      </c>
+    <row r="351" ht="17.55" spans="1:26">
+      <c r="A351" s="2"/>
+      <c r="B351" s="2"/>
       <c r="C351" s="2"/>
       <c r="D351" s="2"/>
       <c r="E351" s="2"/>
@@ -14776,13 +14126,9 @@
       <c r="Y351" s="2"/>
       <c r="Z351" s="2"/>
     </row>
-    <row r="352" ht="68.75" spans="1:26">
-      <c r="A352" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B352" s="1" t="s">
-        <v>186</v>
-      </c>
+    <row r="352" ht="17.55" spans="1:26">
+      <c r="A352" s="2"/>
+      <c r="B352" s="2"/>
       <c r="C352" s="2"/>
       <c r="D352" s="2"/>
       <c r="E352" s="2"/>
@@ -14808,13 +14154,9 @@
       <c r="Y352" s="2"/>
       <c r="Z352" s="2"/>
     </row>
-    <row r="353" ht="84.75" spans="1:26">
-      <c r="A353" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>188</v>
-      </c>
+    <row r="353" ht="17.55" spans="1:26">
+      <c r="A353" s="2"/>
+      <c r="B353" s="2"/>
       <c r="C353" s="2"/>
       <c r="D353" s="2"/>
       <c r="E353" s="2"/>
@@ -14840,13 +14182,9 @@
       <c r="Y353" s="2"/>
       <c r="Z353" s="2"/>
     </row>
-    <row r="354" ht="68.75" spans="1:26">
-      <c r="A354" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>189</v>
-      </c>
+    <row r="354" ht="17.55" spans="1:26">
+      <c r="A354" s="2"/>
+      <c r="B354" s="2"/>
       <c r="C354" s="2"/>
       <c r="D354" s="2"/>
       <c r="E354" s="2"/>
@@ -14872,13 +14210,9 @@
       <c r="Y354" s="2"/>
       <c r="Z354" s="2"/>
     </row>
-    <row r="355" ht="101.75" spans="1:26">
-      <c r="A355" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B355" s="1" t="s">
-        <v>190</v>
-      </c>
+    <row r="355" ht="17.55" spans="1:26">
+      <c r="A355" s="2"/>
+      <c r="B355" s="2"/>
       <c r="C355" s="2"/>
       <c r="D355" s="2"/>
       <c r="E355" s="2"/>
@@ -14904,13 +14238,9 @@
       <c r="Y355" s="2"/>
       <c r="Z355" s="2"/>
     </row>
-    <row r="356" ht="51.75" spans="1:26">
-      <c r="A356" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B356" s="1" t="s">
-        <v>204</v>
-      </c>
+    <row r="356" ht="17.55" spans="1:26">
+      <c r="A356" s="2"/>
+      <c r="B356" s="2"/>
       <c r="C356" s="2"/>
       <c r="D356" s="2"/>
       <c r="E356" s="2"/>
@@ -14936,13 +14266,9 @@
       <c r="Y356" s="2"/>
       <c r="Z356" s="2"/>
     </row>
-    <row r="357" ht="51.75" spans="1:26">
-      <c r="A357" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B357" s="1" t="s">
-        <v>204</v>
-      </c>
+    <row r="357" ht="17.55" spans="1:26">
+      <c r="A357" s="2"/>
+      <c r="B357" s="2"/>
       <c r="C357" s="2"/>
       <c r="D357" s="2"/>
       <c r="E357" s="2"/>
@@ -14968,13 +14294,9 @@
       <c r="Y357" s="2"/>
       <c r="Z357" s="2"/>
     </row>
-    <row r="358" ht="51.75" spans="1:26">
-      <c r="A358" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B358" s="1" t="s">
-        <v>204</v>
-      </c>
+    <row r="358" ht="17.55" spans="1:26">
+      <c r="A358" s="2"/>
+      <c r="B358" s="2"/>
       <c r="C358" s="2"/>
       <c r="D358" s="2"/>
       <c r="E358" s="2"/>
@@ -15000,13 +14322,9 @@
       <c r="Y358" s="2"/>
       <c r="Z358" s="2"/>
     </row>
-    <row r="359" ht="51.75" spans="1:26">
-      <c r="A359" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B359" s="1" t="s">
-        <v>204</v>
-      </c>
+    <row r="359" ht="17.55" spans="1:26">
+      <c r="A359" s="2"/>
+      <c r="B359" s="2"/>
       <c r="C359" s="2"/>
       <c r="D359" s="2"/>
       <c r="E359" s="2"/>
@@ -15032,13 +14350,9 @@
       <c r="Y359" s="2"/>
       <c r="Z359" s="2"/>
     </row>
-    <row r="360" ht="68.75" spans="1:26">
-      <c r="A360" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B360" s="1" t="s">
-        <v>206</v>
-      </c>
+    <row r="360" ht="17.55" spans="1:26">
+      <c r="A360" s="2"/>
+      <c r="B360" s="2"/>
       <c r="C360" s="2"/>
       <c r="D360" s="2"/>
       <c r="E360" s="2"/>
@@ -15064,13 +14378,9 @@
       <c r="Y360" s="2"/>
       <c r="Z360" s="2"/>
     </row>
-    <row r="361" ht="68.75" spans="1:26">
-      <c r="A361" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B361" s="1" t="s">
-        <v>206</v>
-      </c>
+    <row r="361" ht="17.55" spans="1:26">
+      <c r="A361" s="2"/>
+      <c r="B361" s="2"/>
       <c r="C361" s="2"/>
       <c r="D361" s="2"/>
       <c r="E361" s="2"/>
@@ -15096,13 +14406,9 @@
       <c r="Y361" s="2"/>
       <c r="Z361" s="2"/>
     </row>
-    <row r="362" ht="68.75" spans="1:26">
-      <c r="A362" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B362" s="1" t="s">
-        <v>206</v>
-      </c>
+    <row r="362" ht="17.55" spans="1:26">
+      <c r="A362" s="2"/>
+      <c r="B362" s="2"/>
       <c r="C362" s="2"/>
       <c r="D362" s="2"/>
       <c r="E362" s="2"/>
@@ -15128,13 +14434,9 @@
       <c r="Y362" s="2"/>
       <c r="Z362" s="2"/>
     </row>
-    <row r="363" ht="68.75" spans="1:26">
-      <c r="A363" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B363" s="1" t="s">
-        <v>206</v>
-      </c>
+    <row r="363" ht="17.55" spans="1:26">
+      <c r="A363" s="2"/>
+      <c r="B363" s="2"/>
       <c r="C363" s="2"/>
       <c r="D363" s="2"/>
       <c r="E363" s="2"/>
@@ -15160,13 +14462,9 @@
       <c r="Y363" s="2"/>
       <c r="Z363" s="2"/>
     </row>
-    <row r="364" ht="68.75" spans="1:26">
-      <c r="A364" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B364" s="1" t="s">
-        <v>206</v>
-      </c>
+    <row r="364" ht="17.55" spans="1:26">
+      <c r="A364" s="2"/>
+      <c r="B364" s="2"/>
       <c r="C364" s="2"/>
       <c r="D364" s="2"/>
       <c r="E364" s="2"/>
@@ -15192,13 +14490,9 @@
       <c r="Y364" s="2"/>
       <c r="Z364" s="2"/>
     </row>
-    <row r="365" ht="34.75" spans="1:26">
-      <c r="A365" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B365" s="1" t="s">
-        <v>193</v>
-      </c>
+    <row r="365" ht="17.55" spans="1:26">
+      <c r="A365" s="2"/>
+      <c r="B365" s="2"/>
       <c r="C365" s="2"/>
       <c r="D365" s="2"/>
       <c r="E365" s="2"/>
@@ -15224,13 +14518,9 @@
       <c r="Y365" s="2"/>
       <c r="Z365" s="2"/>
     </row>
-    <row r="366" ht="34.75" spans="1:26">
-      <c r="A366" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B366" s="1" t="s">
-        <v>195</v>
-      </c>
+    <row r="366" ht="17.55" spans="1:26">
+      <c r="A366" s="2"/>
+      <c r="B366" s="2"/>
       <c r="C366" s="2"/>
       <c r="D366" s="2"/>
       <c r="E366" s="2"/>
@@ -15256,13 +14546,9 @@
       <c r="Y366" s="2"/>
       <c r="Z366" s="2"/>
     </row>
-    <row r="367" ht="34.75" spans="1:26">
-      <c r="A367" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B367" s="1" t="s">
-        <v>197</v>
-      </c>
+    <row r="367" ht="17.55" spans="1:26">
+      <c r="A367" s="2"/>
+      <c r="B367" s="2"/>
       <c r="C367" s="2"/>
       <c r="D367" s="2"/>
       <c r="E367" s="2"/>
@@ -15288,13 +14574,9 @@
       <c r="Y367" s="2"/>
       <c r="Z367" s="2"/>
     </row>
-    <row r="368" ht="34.75" spans="1:26">
-      <c r="A368" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B368" s="1" t="s">
-        <v>198</v>
-      </c>
+    <row r="368" ht="17.55" spans="1:26">
+      <c r="A368" s="2"/>
+      <c r="B368" s="2"/>
       <c r="C368" s="2"/>
       <c r="D368" s="2"/>
       <c r="E368" s="2"/>
@@ -15320,13 +14602,9 @@
       <c r="Y368" s="2"/>
       <c r="Z368" s="2"/>
     </row>
-    <row r="369" ht="34.75" spans="1:26">
-      <c r="A369" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B369" s="1" t="s">
-        <v>200</v>
-      </c>
+    <row r="369" ht="17.55" spans="1:26">
+      <c r="A369" s="2"/>
+      <c r="B369" s="2"/>
       <c r="C369" s="2"/>
       <c r="D369" s="2"/>
       <c r="E369" s="2"/>
@@ -15352,13 +14630,9 @@
       <c r="Y369" s="2"/>
       <c r="Z369" s="2"/>
     </row>
-    <row r="370" ht="34.75" spans="1:26">
-      <c r="A370" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B370" s="1" t="s">
-        <v>201</v>
-      </c>
+    <row r="370" ht="17.55" spans="1:26">
+      <c r="A370" s="2"/>
+      <c r="B370" s="2"/>
       <c r="C370" s="2"/>
       <c r="D370" s="2"/>
       <c r="E370" s="2"/>
@@ -15384,13 +14658,9 @@
       <c r="Y370" s="2"/>
       <c r="Z370" s="2"/>
     </row>
-    <row r="371" ht="44.75" spans="1:26">
-      <c r="A371" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B371" s="2" t="s">
-        <v>202</v>
-      </c>
+    <row r="371" ht="17.55" spans="1:26">
+      <c r="A371" s="2"/>
+      <c r="B371" s="2"/>
       <c r="C371" s="2"/>
       <c r="D371" s="2"/>
       <c r="E371" s="2"/>
@@ -15416,13 +14686,9 @@
       <c r="Y371" s="2"/>
       <c r="Z371" s="2"/>
     </row>
-    <row r="372" ht="58.75" spans="1:26">
-      <c r="A372" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>54</v>
-      </c>
+    <row r="372" ht="17.55" spans="1:26">
+      <c r="A372" s="2"/>
+      <c r="B372" s="2"/>
       <c r="C372" s="2"/>
       <c r="D372" s="2"/>
       <c r="E372" s="2"/>
@@ -15448,13 +14714,9 @@
       <c r="Y372" s="2"/>
       <c r="Z372" s="2"/>
     </row>
-    <row r="373" ht="44.75" spans="1:26">
-      <c r="A373" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B373" s="2" t="s">
-        <v>149</v>
-      </c>
+    <row r="373" ht="17.55" spans="1:26">
+      <c r="A373" s="2"/>
+      <c r="B373" s="2"/>
       <c r="C373" s="2"/>
       <c r="D373" s="2"/>
       <c r="E373" s="2"/>
@@ -15480,13 +14742,9 @@
       <c r="Y373" s="2"/>
       <c r="Z373" s="2"/>
     </row>
-    <row r="374" ht="58.75" spans="1:26">
-      <c r="A374" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B374" s="2" t="s">
-        <v>203</v>
-      </c>
+    <row r="374" ht="17.55" spans="1:26">
+      <c r="A374" s="2"/>
+      <c r="B374" s="2"/>
       <c r="C374" s="2"/>
       <c r="D374" s="2"/>
       <c r="E374" s="2"/>
@@ -15512,13 +14770,9 @@
       <c r="Y374" s="2"/>
       <c r="Z374" s="2"/>
     </row>
-    <row r="375" ht="44.75" spans="1:26">
-      <c r="A375" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B375" s="2" t="s">
-        <v>205</v>
-      </c>
+    <row r="375" ht="17.55" spans="1:26">
+      <c r="A375" s="2"/>
+      <c r="B375" s="2"/>
       <c r="C375" s="2"/>
       <c r="D375" s="2"/>
       <c r="E375" s="2"/>
@@ -15544,13 +14798,9 @@
       <c r="Y375" s="2"/>
       <c r="Z375" s="2"/>
     </row>
-    <row r="376" ht="58.75" spans="1:26">
-      <c r="A376" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B376" s="2" t="s">
-        <v>207</v>
-      </c>
+    <row r="376" ht="17.55" spans="1:26">
+      <c r="A376" s="2"/>
+      <c r="B376" s="2"/>
       <c r="C376" s="2"/>
       <c r="D376" s="2"/>
       <c r="E376" s="2"/>
@@ -15576,13 +14826,9 @@
       <c r="Y376" s="2"/>
       <c r="Z376" s="2"/>
     </row>
-    <row r="377" ht="29.75" spans="1:26">
-      <c r="A377" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B377" s="2" t="s">
-        <v>208</v>
-      </c>
+    <row r="377" ht="17.55" spans="1:26">
+      <c r="A377" s="2"/>
+      <c r="B377" s="2"/>
       <c r="C377" s="2"/>
       <c r="D377" s="2"/>
       <c r="E377" s="2"/>
@@ -15608,13 +14854,9 @@
       <c r="Y377" s="2"/>
       <c r="Z377" s="2"/>
     </row>
-    <row r="378" ht="29.75" spans="1:26">
-      <c r="A378" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B378" s="2" t="s">
-        <v>209</v>
-      </c>
+    <row r="378" ht="17.55" spans="1:26">
+      <c r="A378" s="2"/>
+      <c r="B378" s="2"/>
       <c r="C378" s="2"/>
       <c r="D378" s="2"/>
       <c r="E378" s="2"/>
@@ -15640,13 +14882,9 @@
       <c r="Y378" s="2"/>
       <c r="Z378" s="2"/>
     </row>
-    <row r="379" ht="29.75" spans="1:26">
-      <c r="A379" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B379" s="2" t="s">
-        <v>210</v>
-      </c>
+    <row r="379" ht="17.55" spans="1:26">
+      <c r="A379" s="2"/>
+      <c r="B379" s="2"/>
       <c r="C379" s="2"/>
       <c r="D379" s="2"/>
       <c r="E379" s="2"/>
@@ -15672,13 +14910,9 @@
       <c r="Y379" s="2"/>
       <c r="Z379" s="2"/>
     </row>
-    <row r="380" ht="29.75" spans="1:26">
-      <c r="A380" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B380" s="2" t="s">
-        <v>211</v>
-      </c>
+    <row r="380" ht="17.55" spans="1:26">
+      <c r="A380" s="2"/>
+      <c r="B380" s="2"/>
       <c r="C380" s="2"/>
       <c r="D380" s="2"/>
       <c r="E380" s="2"/>
@@ -15704,13 +14938,9 @@
       <c r="Y380" s="2"/>
       <c r="Z380" s="2"/>
     </row>
-    <row r="381" ht="44.75" spans="1:26">
-      <c r="A381" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B381" s="2" t="s">
-        <v>212</v>
-      </c>
+    <row r="381" ht="17.55" spans="1:26">
+      <c r="A381" s="2"/>
+      <c r="B381" s="2"/>
       <c r="C381" s="2"/>
       <c r="D381" s="2"/>
       <c r="E381" s="2"/>
@@ -15736,13 +14966,9 @@
       <c r="Y381" s="2"/>
       <c r="Z381" s="2"/>
     </row>
-    <row r="382" ht="29.75" spans="1:26">
-      <c r="A382" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B382" s="2" t="s">
-        <v>213</v>
-      </c>
+    <row r="382" ht="17.55" spans="1:26">
+      <c r="A382" s="2"/>
+      <c r="B382" s="2"/>
       <c r="C382" s="2"/>
       <c r="D382" s="2"/>
       <c r="E382" s="2"/>
@@ -15768,13 +14994,9 @@
       <c r="Y382" s="2"/>
       <c r="Z382" s="2"/>
     </row>
-    <row r="383" ht="29.75" spans="1:26">
-      <c r="A383" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B383" s="2" t="s">
-        <v>214</v>
-      </c>
+    <row r="383" ht="17.55" spans="1:26">
+      <c r="A383" s="2"/>
+      <c r="B383" s="2"/>
       <c r="C383" s="2"/>
       <c r="D383" s="2"/>
       <c r="E383" s="2"/>
@@ -15800,13 +15022,9 @@
       <c r="Y383" s="2"/>
       <c r="Z383" s="2"/>
     </row>
-    <row r="384" ht="58.75" spans="1:26">
-      <c r="A384" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B384" s="2" t="s">
-        <v>152</v>
-      </c>
+    <row r="384" ht="17.55" spans="1:26">
+      <c r="A384" s="2"/>
+      <c r="B384" s="2"/>
       <c r="C384" s="2"/>
       <c r="D384" s="2"/>
       <c r="E384" s="2"/>
@@ -15832,13 +15050,9 @@
       <c r="Y384" s="2"/>
       <c r="Z384" s="2"/>
     </row>
-    <row r="385" ht="58.75" spans="1:26">
-      <c r="A385" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B385" s="2" t="s">
-        <v>215</v>
-      </c>
+    <row r="385" ht="17.55" spans="1:26">
+      <c r="A385" s="2"/>
+      <c r="B385" s="2"/>
       <c r="C385" s="2"/>
       <c r="D385" s="2"/>
       <c r="E385" s="2"/>
@@ -15864,13 +15078,9 @@
       <c r="Y385" s="2"/>
       <c r="Z385" s="2"/>
     </row>
-    <row r="386" ht="44.75" spans="1:26">
-      <c r="A386" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B386" s="2" t="s">
-        <v>216</v>
-      </c>
+    <row r="386" ht="17.55" spans="1:26">
+      <c r="A386" s="2"/>
+      <c r="B386" s="2"/>
       <c r="C386" s="2"/>
       <c r="D386" s="2"/>
       <c r="E386" s="2"/>
@@ -15896,13 +15106,9 @@
       <c r="Y386" s="2"/>
       <c r="Z386" s="2"/>
     </row>
-    <row r="387" ht="58.75" spans="1:26">
-      <c r="A387" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B387" s="2" t="s">
-        <v>41</v>
-      </c>
+    <row r="387" ht="17.55" spans="1:26">
+      <c r="A387" s="2"/>
+      <c r="B387" s="2"/>
       <c r="C387" s="2"/>
       <c r="D387" s="2"/>
       <c r="E387" s="2"/>
@@ -15928,13 +15134,9 @@
       <c r="Y387" s="2"/>
       <c r="Z387" s="2"/>
     </row>
-    <row r="388" ht="44.75" spans="1:26">
-      <c r="A388" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B388" s="2" t="s">
-        <v>217</v>
-      </c>
+    <row r="388" ht="17.55" spans="1:26">
+      <c r="A388" s="2"/>
+      <c r="B388" s="2"/>
       <c r="C388" s="2"/>
       <c r="D388" s="2"/>
       <c r="E388" s="2"/>
@@ -15960,13 +15162,9 @@
       <c r="Y388" s="2"/>
       <c r="Z388" s="2"/>
     </row>
-    <row r="389" ht="58.75" spans="1:26">
-      <c r="A389" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B389" s="2" t="s">
-        <v>219</v>
-      </c>
+    <row r="389" ht="17.55" spans="1:26">
+      <c r="A389" s="2"/>
+      <c r="B389" s="2"/>
       <c r="C389" s="2"/>
       <c r="D389" s="2"/>
       <c r="E389" s="2"/>
@@ -15992,13 +15190,9 @@
       <c r="Y389" s="2"/>
       <c r="Z389" s="2"/>
     </row>
-    <row r="390" ht="29.75" spans="1:26">
-      <c r="A390" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B390" s="2" t="s">
-        <v>239</v>
-      </c>
+    <row r="390" ht="17.55" spans="1:26">
+      <c r="A390" s="2"/>
+      <c r="B390" s="2"/>
       <c r="C390" s="2"/>
       <c r="D390" s="2"/>
       <c r="E390" s="2"/>
@@ -16024,13 +15218,9 @@
       <c r="Y390" s="2"/>
       <c r="Z390" s="2"/>
     </row>
-    <row r="391" ht="29.75" spans="1:26">
-      <c r="A391" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B391" s="2" t="s">
-        <v>221</v>
-      </c>
+    <row r="391" ht="17.55" spans="1:26">
+      <c r="A391" s="2"/>
+      <c r="B391" s="2"/>
       <c r="C391" s="2"/>
       <c r="D391" s="2"/>
       <c r="E391" s="2"/>
@@ -16056,13 +15246,9 @@
       <c r="Y391" s="2"/>
       <c r="Z391" s="2"/>
     </row>
-    <row r="392" ht="29.75" spans="1:26">
-      <c r="A392" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B392" s="2" t="s">
-        <v>222</v>
-      </c>
+    <row r="392" ht="17.55" spans="1:26">
+      <c r="A392" s="2"/>
+      <c r="B392" s="2"/>
       <c r="C392" s="2"/>
       <c r="D392" s="2"/>
       <c r="E392" s="2"/>
@@ -16088,13 +15274,9 @@
       <c r="Y392" s="2"/>
       <c r="Z392" s="2"/>
     </row>
-    <row r="393" ht="44.75" spans="1:26">
-      <c r="A393" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B393" s="2" t="s">
-        <v>219</v>
-      </c>
+    <row r="393" ht="17.55" spans="1:26">
+      <c r="A393" s="2"/>
+      <c r="B393" s="2"/>
       <c r="C393" s="2"/>
       <c r="D393" s="2"/>
       <c r="E393" s="2"/>
@@ -16120,13 +15302,9 @@
       <c r="Y393" s="2"/>
       <c r="Z393" s="2"/>
     </row>
-    <row r="394" ht="44.75" spans="1:26">
-      <c r="A394" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B394" s="2" t="s">
-        <v>223</v>
-      </c>
+    <row r="394" ht="17.55" spans="1:26">
+      <c r="A394" s="2"/>
+      <c r="B394" s="2"/>
       <c r="C394" s="2"/>
       <c r="D394" s="2"/>
       <c r="E394" s="2"/>
@@ -16152,13 +15330,9 @@
       <c r="Y394" s="2"/>
       <c r="Z394" s="2"/>
     </row>
-    <row r="395" ht="58.75" spans="1:26">
-      <c r="A395" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B395" s="2" t="s">
-        <v>233</v>
-      </c>
+    <row r="395" ht="17.55" spans="1:26">
+      <c r="A395" s="2"/>
+      <c r="B395" s="2"/>
       <c r="C395" s="2"/>
       <c r="D395" s="2"/>
       <c r="E395" s="2"/>
@@ -16184,13 +15358,9 @@
       <c r="Y395" s="2"/>
       <c r="Z395" s="2"/>
     </row>
-    <row r="396" ht="44.75" spans="1:26">
-      <c r="A396" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B396" s="2" t="s">
-        <v>236</v>
-      </c>
+    <row r="396" ht="17.55" spans="1:26">
+      <c r="A396" s="2"/>
+      <c r="B396" s="2"/>
       <c r="C396" s="2"/>
       <c r="D396" s="2"/>
       <c r="E396" s="2"/>
@@ -16216,13 +15386,9 @@
       <c r="Y396" s="2"/>
       <c r="Z396" s="2"/>
     </row>
-    <row r="397" ht="44.75" spans="1:26">
-      <c r="A397" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B397" s="2" t="s">
-        <v>224</v>
-      </c>
+    <row r="397" ht="17.55" spans="1:26">
+      <c r="A397" s="2"/>
+      <c r="B397" s="2"/>
       <c r="C397" s="2"/>
       <c r="D397" s="2"/>
       <c r="E397" s="2"/>
@@ -16248,13 +15414,9 @@
       <c r="Y397" s="2"/>
       <c r="Z397" s="2"/>
     </row>
-    <row r="398" ht="58.75" spans="1:26">
-      <c r="A398" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B398" s="2" t="s">
-        <v>224</v>
-      </c>
+    <row r="398" ht="17.55" spans="1:26">
+      <c r="A398" s="2"/>
+      <c r="B398" s="2"/>
       <c r="C398" s="2"/>
       <c r="D398" s="2"/>
       <c r="E398" s="2"/>
@@ -16280,13 +15442,9 @@
       <c r="Y398" s="2"/>
       <c r="Z398" s="2"/>
     </row>
-    <row r="399" ht="29.75" spans="1:26">
-      <c r="A399" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B399" s="2" t="s">
-        <v>225</v>
-      </c>
+    <row r="399" ht="17.55" spans="1:26">
+      <c r="A399" s="2"/>
+      <c r="B399" s="2"/>
       <c r="C399" s="2"/>
       <c r="D399" s="2"/>
       <c r="E399" s="2"/>
@@ -16312,13 +15470,9 @@
       <c r="Y399" s="2"/>
       <c r="Z399" s="2"/>
     </row>
-    <row r="400" ht="44.75" spans="1:26">
-      <c r="A400" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B400" s="2" t="s">
-        <v>225</v>
-      </c>
+    <row r="400" ht="17.55" spans="1:26">
+      <c r="A400" s="2"/>
+      <c r="B400" s="2"/>
       <c r="C400" s="2"/>
       <c r="D400" s="2"/>
       <c r="E400" s="2"/>
@@ -16344,13 +15498,9 @@
       <c r="Y400" s="2"/>
       <c r="Z400" s="2"/>
     </row>
-    <row r="401" ht="29.75" spans="1:26">
-      <c r="A401" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B401" s="2" t="s">
-        <v>227</v>
-      </c>
+    <row r="401" ht="17.55" spans="1:26">
+      <c r="A401" s="2"/>
+      <c r="B401" s="2"/>
       <c r="C401" s="2"/>
       <c r="D401" s="2"/>
       <c r="E401" s="2"/>
@@ -16376,13 +15526,9 @@
       <c r="Y401" s="2"/>
       <c r="Z401" s="2"/>
     </row>
-    <row r="402" ht="44.75" spans="1:26">
-      <c r="A402" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B402" s="2" t="s">
-        <v>227</v>
-      </c>
+    <row r="402" ht="17.55" spans="1:26">
+      <c r="A402" s="2"/>
+      <c r="B402" s="2"/>
       <c r="C402" s="2"/>
       <c r="D402" s="2"/>
       <c r="E402" s="2"/>
@@ -16408,13 +15554,9 @@
       <c r="Y402" s="2"/>
       <c r="Z402" s="2"/>
     </row>
-    <row r="403" ht="44.75" spans="1:26">
-      <c r="A403" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B403" s="2" t="s">
-        <v>228</v>
-      </c>
+    <row r="403" ht="17.55" spans="1:26">
+      <c r="A403" s="2"/>
+      <c r="B403" s="2"/>
       <c r="C403" s="2"/>
       <c r="D403" s="2"/>
       <c r="E403" s="2"/>
@@ -16441,12 +15583,8 @@
       <c r="Z403" s="2"/>
     </row>
     <row r="404" ht="17.55" spans="1:26">
-      <c r="A404" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B404" s="2" t="s">
-        <v>229</v>
-      </c>
+      <c r="A404" s="2"/>
+      <c r="B404" s="2"/>
       <c r="C404" s="2"/>
       <c r="D404" s="2"/>
       <c r="E404" s="2"/>
@@ -16472,13 +15610,9 @@
       <c r="Y404" s="2"/>
       <c r="Z404" s="2"/>
     </row>
-    <row r="405" ht="29.75" spans="1:26">
-      <c r="A405" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B405" s="2" t="s">
-        <v>229</v>
-      </c>
+    <row r="405" ht="17.55" spans="1:26">
+      <c r="A405" s="2"/>
+      <c r="B405" s="2"/>
       <c r="C405" s="2"/>
       <c r="D405" s="2"/>
       <c r="E405" s="2"/>
@@ -16504,13 +15638,9 @@
       <c r="Y405" s="2"/>
       <c r="Z405" s="2"/>
     </row>
-    <row r="406" ht="29.75" spans="1:26">
-      <c r="A406" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B406" s="2" t="s">
-        <v>230</v>
-      </c>
+    <row r="406" ht="17.55" spans="1:26">
+      <c r="A406" s="2"/>
+      <c r="B406" s="2"/>
       <c r="C406" s="2"/>
       <c r="D406" s="2"/>
       <c r="E406" s="2"/>
@@ -16536,13 +15666,9 @@
       <c r="Y406" s="2"/>
       <c r="Z406" s="2"/>
     </row>
-    <row r="407" ht="44.75" spans="1:26">
-      <c r="A407" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B407" s="2" t="s">
-        <v>98</v>
-      </c>
+    <row r="407" ht="17.55" spans="1:26">
+      <c r="A407" s="2"/>
+      <c r="B407" s="2"/>
       <c r="C407" s="2"/>
       <c r="D407" s="2"/>
       <c r="E407" s="2"/>
@@ -16568,13 +15694,9 @@
       <c r="Y407" s="2"/>
       <c r="Z407" s="2"/>
     </row>
-    <row r="408" ht="44.75" spans="1:26">
-      <c r="A408" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B408" s="2" t="s">
-        <v>231</v>
-      </c>
+    <row r="408" ht="17.55" spans="1:26">
+      <c r="A408" s="2"/>
+      <c r="B408" s="2"/>
       <c r="C408" s="2"/>
       <c r="D408" s="2"/>
       <c r="E408" s="2"/>
@@ -16600,13 +15722,9 @@
       <c r="Y408" s="2"/>
       <c r="Z408" s="2"/>
     </row>
-    <row r="409" ht="58.75" spans="1:26">
-      <c r="A409" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B409" s="2" t="s">
-        <v>231</v>
-      </c>
+    <row r="409" ht="17.55" spans="1:26">
+      <c r="A409" s="2"/>
+      <c r="B409" s="2"/>
       <c r="C409" s="2"/>
       <c r="D409" s="2"/>
       <c r="E409" s="2"/>
@@ -16632,13 +15750,9 @@
       <c r="Y409" s="2"/>
       <c r="Z409" s="2"/>
     </row>
-    <row r="410" ht="44.75" spans="1:26">
-      <c r="A410" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B410" s="2" t="s">
-        <v>247</v>
-      </c>
+    <row r="410" ht="17.55" spans="1:26">
+      <c r="A410" s="2"/>
+      <c r="B410" s="2"/>
       <c r="C410" s="2"/>
       <c r="D410" s="2"/>
       <c r="E410" s="2"/>
@@ -16664,13 +15778,9 @@
       <c r="Y410" s="2"/>
       <c r="Z410" s="2"/>
     </row>
-    <row r="411" ht="44.75" spans="1:26">
-      <c r="A411" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B411" s="2" t="s">
-        <v>232</v>
-      </c>
+    <row r="411" ht="17.55" spans="1:26">
+      <c r="A411" s="2"/>
+      <c r="B411" s="2"/>
       <c r="C411" s="2"/>
       <c r="D411" s="2"/>
       <c r="E411" s="2"/>
@@ -16696,13 +15806,9 @@
       <c r="Y411" s="2"/>
       <c r="Z411" s="2"/>
     </row>
-    <row r="412" ht="58.75" spans="1:26">
-      <c r="A412" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B412" s="2" t="s">
-        <v>228</v>
-      </c>
+    <row r="412" ht="17.55" spans="1:26">
+      <c r="A412" s="2"/>
+      <c r="B412" s="2"/>
       <c r="C412" s="2"/>
       <c r="D412" s="2"/>
       <c r="E412" s="2"/>
@@ -16728,13 +15834,9 @@
       <c r="Y412" s="2"/>
       <c r="Z412" s="2"/>
     </row>
-    <row r="413" ht="29.75" spans="1:26">
-      <c r="A413" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B413" s="2" t="s">
-        <v>234</v>
-      </c>
+    <row r="413" ht="17.55" spans="1:26">
+      <c r="A413" s="2"/>
+      <c r="B413" s="2"/>
       <c r="C413" s="2"/>
       <c r="D413" s="2"/>
       <c r="E413" s="2"/>
@@ -16760,13 +15862,9 @@
       <c r="Y413" s="2"/>
       <c r="Z413" s="2"/>
     </row>
-    <row r="414" ht="29.75" spans="1:26">
-      <c r="A414" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B414" s="2" t="s">
-        <v>237</v>
-      </c>
+    <row r="414" ht="17.55" spans="1:26">
+      <c r="A414" s="2"/>
+      <c r="B414" s="2"/>
       <c r="C414" s="2"/>
       <c r="D414" s="2"/>
       <c r="E414" s="2"/>
@@ -16793,12 +15891,8 @@
       <c r="Z414" s="2"/>
     </row>
     <row r="415" ht="17.55" spans="1:26">
-      <c r="A415" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B415" s="2" t="s">
-        <v>240</v>
-      </c>
+      <c r="A415" s="2"/>
+      <c r="B415" s="2"/>
       <c r="C415" s="2"/>
       <c r="D415" s="2"/>
       <c r="E415" s="2"/>
@@ -16824,13 +15918,9 @@
       <c r="Y415" s="2"/>
       <c r="Z415" s="2"/>
     </row>
-    <row r="416" ht="29.75" spans="1:26">
-      <c r="A416" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B416" s="2" t="s">
-        <v>241</v>
-      </c>
+    <row r="416" ht="17.55" spans="1:26">
+      <c r="A416" s="2"/>
+      <c r="B416" s="2"/>
       <c r="C416" s="2"/>
       <c r="D416" s="2"/>
       <c r="E416" s="2"/>
@@ -16856,13 +15946,9 @@
       <c r="Y416" s="2"/>
       <c r="Z416" s="2"/>
     </row>
-    <row r="417" ht="58.75" spans="1:26">
-      <c r="A417" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>242</v>
-      </c>
+    <row r="417" ht="17.55" spans="1:26">
+      <c r="A417" s="2"/>
+      <c r="B417" s="2"/>
       <c r="C417" s="2"/>
       <c r="D417" s="2"/>
       <c r="E417" s="2"/>
@@ -16888,13 +15974,9 @@
       <c r="Y417" s="2"/>
       <c r="Z417" s="2"/>
     </row>
-    <row r="418" ht="58.75" spans="1:26">
-      <c r="A418" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B418" s="2" t="s">
-        <v>244</v>
-      </c>
+    <row r="418" ht="17.55" spans="1:26">
+      <c r="A418" s="2"/>
+      <c r="B418" s="2"/>
       <c r="C418" s="2"/>
       <c r="D418" s="2"/>
       <c r="E418" s="2"/>
@@ -16920,13 +16002,9 @@
       <c r="Y418" s="2"/>
       <c r="Z418" s="2"/>
     </row>
-    <row r="419" ht="44.75" spans="1:26">
-      <c r="A419" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B419" s="2" t="s">
-        <v>248</v>
-      </c>
+    <row r="419" ht="17.55" spans="1:26">
+      <c r="A419" s="2"/>
+      <c r="B419" s="2"/>
       <c r="C419" s="2"/>
       <c r="D419" s="2"/>
       <c r="E419" s="2"/>
@@ -16952,13 +16030,9 @@
       <c r="Y419" s="2"/>
       <c r="Z419" s="2"/>
     </row>
-    <row r="420" ht="72.75" spans="1:26">
-      <c r="A420" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B420" s="2" t="s">
-        <v>250</v>
-      </c>
+    <row r="420" ht="17.55" spans="1:26">
+      <c r="A420" s="2"/>
+      <c r="B420" s="2"/>
       <c r="C420" s="2"/>
       <c r="D420" s="2"/>
       <c r="E420" s="2"/>
@@ -16984,13 +16058,9 @@
       <c r="Y420" s="2"/>
       <c r="Z420" s="2"/>
     </row>
-    <row r="421" ht="44.75" spans="1:26">
-      <c r="A421" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B421" s="2" t="s">
-        <v>160</v>
-      </c>
+    <row r="421" ht="17.55" spans="1:26">
+      <c r="A421" s="2"/>
+      <c r="B421" s="2"/>
       <c r="C421" s="2"/>
       <c r="D421" s="2"/>
       <c r="E421" s="2"/>
